--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -7336,7 +7336,7 @@
         <v>67438068</v>
       </c>
       <c r="B50" t="n">
-        <v>90233</v>
+        <v>90243</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -7336,7 +7336,7 @@
         <v>67438068</v>
       </c>
       <c r="B50" t="n">
-        <v>90243</v>
+        <v>90255</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -7336,7 +7336,7 @@
         <v>67438068</v>
       </c>
       <c r="B50" t="n">
-        <v>90255</v>
+        <v>90256</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -7336,7 +7336,7 @@
         <v>67438068</v>
       </c>
       <c r="B50" t="n">
-        <v>90256</v>
+        <v>90259</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -7336,7 +7336,7 @@
         <v>67438068</v>
       </c>
       <c r="B50" t="n">
-        <v>90259</v>
+        <v>90265</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -7336,7 +7336,7 @@
         <v>67438068</v>
       </c>
       <c r="B50" t="n">
-        <v>90265</v>
+        <v>90266</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -7336,7 +7336,7 @@
         <v>67438068</v>
       </c>
       <c r="B50" t="n">
-        <v>90266</v>
+        <v>90273</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY69"/>
+  <dimension ref="A1:AY68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9044,10 +9044,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112144417</v>
+        <v>112144281</v>
       </c>
       <c r="B63" t="n">
-        <v>78686</v>
+        <v>90874</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -9060,33 +9060,25 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6456</v>
+        <v>5964</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Sarcodon imbricatus s.str.</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J63" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
       <c r="K63" t="inlineStr"/>
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
@@ -9095,10 +9087,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>492336</v>
+        <v>492208</v>
       </c>
       <c r="R63" t="n">
-        <v>6678741</v>
+        <v>6678843</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -9155,17 +9147,17 @@
       </c>
       <c r="AJ63" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK63" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -9183,10 +9175,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112144281</v>
+        <v>112144721</v>
       </c>
       <c r="B64" t="n">
-        <v>90874</v>
+        <v>89096</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -9195,29 +9187,37 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5964</v>
+        <v>720</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus s.str.</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
@@ -9226,10 +9226,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>492208</v>
+        <v>492322</v>
       </c>
       <c r="R64" t="n">
-        <v>6678843</v>
+        <v>6678801</v>
       </c>
       <c r="S64" t="n">
         <v>5</v>
@@ -9314,10 +9314,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112144721</v>
+        <v>112144205</v>
       </c>
       <c r="B65" t="n">
-        <v>89096</v>
+        <v>90519</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -9326,30 +9326,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>720</v>
+        <v>4769</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Svavelriska</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Lactarius scrobiculatus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Scop.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -9365,10 +9365,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>492322</v>
+        <v>492253</v>
       </c>
       <c r="R65" t="n">
-        <v>6678801</v>
+        <v>6678916</v>
       </c>
       <c r="S65" t="n">
         <v>5</v>
@@ -9453,10 +9453,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112144205</v>
+        <v>112144296</v>
       </c>
       <c r="B66" t="n">
-        <v>90519</v>
+        <v>89053</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -9469,33 +9469,25 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>4769</v>
+        <v>4189</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Kamjordstjärna</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Geastrum pectinatum</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
@@ -9504,10 +9496,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>492253</v>
+        <v>492208</v>
       </c>
       <c r="R66" t="n">
-        <v>6678916</v>
+        <v>6678843</v>
       </c>
       <c r="S66" t="n">
         <v>5</v>
@@ -9574,7 +9566,7 @@
       </c>
       <c r="AO66" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>barrmatta under gran # Picea abies</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -9592,10 +9584,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112144296</v>
+        <v>112144729</v>
       </c>
       <c r="B67" t="n">
-        <v>89053</v>
+        <v>99924</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -9608,26 +9600,27 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4189</v>
+        <v>221235</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Kamjordstjärna</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Geastrum pectinatum</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Pers.:Pers.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="J67" t="inlineStr"/>
       <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
@@ -9635,10 +9628,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>492208</v>
+        <v>492322</v>
       </c>
       <c r="R67" t="n">
-        <v>6678843</v>
+        <v>6678801</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -9691,21 +9684,6 @@
       <c r="AI67" t="inlineStr">
         <is>
           <t>stråk med lågört</t>
-        </is>
-      </c>
-      <c r="AJ67" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK67" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO67" t="inlineStr">
-        <is>
-          <t>barrmatta under gran # Picea abies</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -9723,10 +9701,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112144729</v>
+        <v>112144838</v>
       </c>
       <c r="B68" t="n">
-        <v>99924</v>
+        <v>89096</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -9735,31 +9713,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>221235</v>
+        <v>720</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
-      <c r="J68" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
@@ -9767,7 +9752,7 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>492322</v>
+        <v>492348</v>
       </c>
       <c r="R68" t="n">
         <v>6678801</v>
@@ -9820,11 +9805,6 @@
           <t>Lågörtgranskog</t>
         </is>
       </c>
-      <c r="AI68" t="inlineStr">
-        <is>
-          <t>stråk med lågört</t>
-        </is>
-      </c>
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
@@ -9837,125 +9817,6 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
-    </row>
-    <row r="69">
-      <c r="A69" t="n">
-        <v>112144838</v>
-      </c>
-      <c r="B69" t="n">
-        <v>89096</v>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>720</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>Violgubbe</t>
-        </is>
-      </c>
-      <c r="G69" t="inlineStr">
-        <is>
-          <t>Gomphus clavatus</t>
-        </is>
-      </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J69" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
-      <c r="K69" t="inlineStr"/>
-      <c r="N69" t="inlineStr"/>
-      <c r="P69" t="inlineStr">
-        <is>
-          <t>Norsådammen, Dlr</t>
-        </is>
-      </c>
-      <c r="Q69" t="n">
-        <v>492348</v>
-      </c>
-      <c r="R69" t="n">
-        <v>6678801</v>
-      </c>
-      <c r="S69" t="n">
-        <v>5</v>
-      </c>
-      <c r="T69" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
-        <is>
-          <t>Ludvika</t>
-        </is>
-      </c>
-      <c r="V69" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W69" t="inlineStr">
-        <is>
-          <t>Grangärde</t>
-        </is>
-      </c>
-      <c r="Y69" t="inlineStr">
-        <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="AA69" t="inlineStr">
-        <is>
-          <t>2023-09-14</t>
-        </is>
-      </c>
-      <c r="AD69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF69" t="inlineStr"/>
-      <c r="AG69" t="b">
-        <v>0</v>
-      </c>
-      <c r="AH69" t="inlineStr">
-        <is>
-          <t>Lågörtgranskog</t>
-        </is>
-      </c>
-      <c r="AT69" t="inlineStr"/>
-      <c r="AW69" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>Janolof Hermansson</t>
-        </is>
-      </c>
-      <c r="AY69" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY68"/>
+  <dimension ref="A1:AY78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -9818,6 +9818,1066 @@
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>125995167</v>
+      </c>
+      <c r="B69" t="n">
+        <v>100513</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>492326</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6678848</v>
+      </c>
+      <c r="S69" t="n">
+        <v>15</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>125995080</v>
+      </c>
+      <c r="B70" t="n">
+        <v>91989</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>366</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Norsdammen, Norsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>492347</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6678900</v>
+      </c>
+      <c r="S70" t="n">
+        <v>15</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>125995614</v>
+      </c>
+      <c r="B71" t="n">
+        <v>91227</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>492268</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6678870</v>
+      </c>
+      <c r="S71" t="n">
+        <v>15</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>125995168</v>
+      </c>
+      <c r="B72" t="n">
+        <v>100420</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>492326</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6678848</v>
+      </c>
+      <c r="S72" t="n">
+        <v>15</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>125995373</v>
+      </c>
+      <c r="B73" t="n">
+        <v>91280</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>5321</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Barkticka</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Oxyporus corticola</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Fr.) Ryvarden</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>492326</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6678848</v>
+      </c>
+      <c r="S73" t="n">
+        <v>15</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>125995636</v>
+      </c>
+      <c r="B74" t="n">
+        <v>91241</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>1204</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Gränsticka</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Phellopilus nigrolimitatus</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>492266</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6678873</v>
+      </c>
+      <c r="S74" t="n">
+        <v>15</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>125995313</v>
+      </c>
+      <c r="B75" t="n">
+        <v>102833</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>222002</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Underviol</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Viola mirabilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>492326</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6678848</v>
+      </c>
+      <c r="S75" t="n">
+        <v>15</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>125995622</v>
+      </c>
+      <c r="B76" t="n">
+        <v>91582</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>492268</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6678870</v>
+      </c>
+      <c r="S76" t="n">
+        <v>15</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>125995215</v>
+      </c>
+      <c r="B77" t="n">
+        <v>101417</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>221235</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Vårärt</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Lathyrus vernus</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) Bernh.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>492326</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6678848</v>
+      </c>
+      <c r="S77" t="n">
+        <v>15</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Andreas Öster, Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>125995418</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79974</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>492332</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6678856</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Anton Björk, Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9820,32 +9820,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125995167</v>
+        <v>125995614</v>
       </c>
       <c r="B69" t="n">
-        <v>100513</v>
+        <v>91228</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9855,10 +9855,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492326</v>
+        <v>492268</v>
       </c>
       <c r="R69" t="n">
-        <v>6678848</v>
+        <v>6678870</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9927,45 +9927,45 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125995080</v>
+        <v>125995167</v>
       </c>
       <c r="B70" t="n">
-        <v>91989</v>
+        <v>100514</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>366</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norsdammen, Norsdammen, Dlr</t>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492347</v>
+        <v>492326</v>
       </c>
       <c r="R70" t="n">
-        <v>6678900</v>
+        <v>6678848</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10034,10 +10034,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125995614</v>
+        <v>125995080</v>
       </c>
       <c r="B71" t="n">
-        <v>91227</v>
+        <v>91990</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10045,34 +10045,34 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norsbodarna, Norsbodarna, Dlr</t>
+          <t>Norsdammen, Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492268</v>
+        <v>492347</v>
       </c>
       <c r="R71" t="n">
-        <v>6678870</v>
+        <v>6678900</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10141,10 +10141,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125995168</v>
+        <v>125995373</v>
       </c>
       <c r="B72" t="n">
-        <v>100420</v>
+        <v>91281</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10152,21 +10152,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222771</v>
+        <v>5321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10248,10 +10248,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125995373</v>
+        <v>125995168</v>
       </c>
       <c r="B73" t="n">
-        <v>91280</v>
+        <v>100421</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10259,21 +10259,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5321</v>
+        <v>222771</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
         <v>125995636</v>
       </c>
       <c r="B74" t="n">
-        <v>91241</v>
+        <v>91242</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>125995313</v>
       </c>
       <c r="B75" t="n">
-        <v>102833</v>
+        <v>102834</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>125995622</v>
       </c>
       <c r="B76" t="n">
-        <v>91582</v>
+        <v>91583</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>125995215</v>
       </c>
       <c r="B77" t="n">
-        <v>101417</v>
+        <v>101418</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>125995418</v>
       </c>
       <c r="B78" t="n">
-        <v>79974</v>
+        <v>79975</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9820,10 +9820,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125995614</v>
+        <v>125995080</v>
       </c>
       <c r="B69" t="n">
-        <v>91228</v>
+        <v>91993</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9831,34 +9831,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norsbodarna, Norsbodarna, Dlr</t>
+          <t>Norsdammen, Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492268</v>
+        <v>492347</v>
       </c>
       <c r="R69" t="n">
-        <v>6678870</v>
+        <v>6678900</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9927,32 +9927,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125995167</v>
+        <v>125995614</v>
       </c>
       <c r="B70" t="n">
-        <v>100514</v>
+        <v>91228</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9962,10 +9962,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492326</v>
+        <v>492268</v>
       </c>
       <c r="R70" t="n">
-        <v>6678848</v>
+        <v>6678870</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10034,45 +10034,45 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125995080</v>
+        <v>125995167</v>
       </c>
       <c r="B71" t="n">
-        <v>91990</v>
+        <v>100516</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>366</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Norsdammen, Norsdammen, Dlr</t>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492347</v>
+        <v>492326</v>
       </c>
       <c r="R71" t="n">
-        <v>6678900</v>
+        <v>6678848</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10141,10 +10141,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125995373</v>
+        <v>125995168</v>
       </c>
       <c r="B72" t="n">
-        <v>91281</v>
+        <v>100423</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10152,21 +10152,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5321</v>
+        <v>222771</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10248,10 +10248,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125995168</v>
+        <v>125995373</v>
       </c>
       <c r="B73" t="n">
-        <v>100421</v>
+        <v>91281</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10259,21 +10259,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222771</v>
+        <v>5321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10465,7 +10465,7 @@
         <v>125995313</v>
       </c>
       <c r="B75" t="n">
-        <v>102834</v>
+        <v>102836</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -10572,7 +10572,7 @@
         <v>125995622</v>
       </c>
       <c r="B76" t="n">
-        <v>91583</v>
+        <v>91586</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>125995215</v>
       </c>
       <c r="B77" t="n">
-        <v>101418</v>
+        <v>101420</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9820,45 +9820,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125995080</v>
+        <v>125995167</v>
       </c>
       <c r="B69" t="n">
-        <v>91993</v>
+        <v>100520</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>366</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norsdammen, Norsdammen, Dlr</t>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492347</v>
+        <v>492326</v>
       </c>
       <c r="R69" t="n">
-        <v>6678900</v>
+        <v>6678848</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9927,10 +9927,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125995614</v>
+        <v>125995080</v>
       </c>
       <c r="B70" t="n">
-        <v>91228</v>
+        <v>91997</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9938,34 +9938,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norsbodarna, Norsbodarna, Dlr</t>
+          <t>Norsdammen, Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492268</v>
+        <v>492347</v>
       </c>
       <c r="R70" t="n">
-        <v>6678870</v>
+        <v>6678900</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10034,32 +10034,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125995167</v>
+        <v>125995614</v>
       </c>
       <c r="B71" t="n">
-        <v>100516</v>
+        <v>91232</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492326</v>
+        <v>492268</v>
       </c>
       <c r="R71" t="n">
-        <v>6678848</v>
+        <v>6678870</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10141,10 +10141,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125995168</v>
+        <v>125995373</v>
       </c>
       <c r="B72" t="n">
-        <v>100423</v>
+        <v>91285</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10152,21 +10152,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222771</v>
+        <v>5321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10248,10 +10248,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125995373</v>
+        <v>125995168</v>
       </c>
       <c r="B73" t="n">
-        <v>91281</v>
+        <v>100427</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10259,21 +10259,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5321</v>
+        <v>222771</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
         <v>125995636</v>
       </c>
       <c r="B74" t="n">
-        <v>91242</v>
+        <v>91246</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>125995313</v>
       </c>
       <c r="B75" t="n">
-        <v>102836</v>
+        <v>102840</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>125995622</v>
       </c>
       <c r="B76" t="n">
-        <v>91586</v>
+        <v>91590</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>125995215</v>
       </c>
       <c r="B77" t="n">
-        <v>101420</v>
+        <v>101424</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>125995418</v>
       </c>
       <c r="B78" t="n">
-        <v>79975</v>
+        <v>79979</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9820,45 +9820,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125995167</v>
+        <v>125995080</v>
       </c>
       <c r="B69" t="n">
-        <v>100520</v>
+        <v>91997</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norsbodarna, Norsbodarna, Dlr</t>
+          <t>Norsdammen, Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492326</v>
+        <v>492347</v>
       </c>
       <c r="R69" t="n">
-        <v>6678848</v>
+        <v>6678900</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9927,10 +9927,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125995080</v>
+        <v>125995614</v>
       </c>
       <c r="B70" t="n">
-        <v>91997</v>
+        <v>91232</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9938,34 +9938,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norsdammen, Norsdammen, Dlr</t>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492347</v>
+        <v>492268</v>
       </c>
       <c r="R70" t="n">
-        <v>6678900</v>
+        <v>6678870</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10034,32 +10034,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125995614</v>
+        <v>125995167</v>
       </c>
       <c r="B71" t="n">
-        <v>91232</v>
+        <v>100520</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492268</v>
+        <v>492326</v>
       </c>
       <c r="R71" t="n">
-        <v>6678870</v>
+        <v>6678848</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9820,45 +9820,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125995080</v>
+        <v>125995167</v>
       </c>
       <c r="B69" t="n">
-        <v>91997</v>
+        <v>100521</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>366</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norsdammen, Norsdammen, Dlr</t>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492347</v>
+        <v>492326</v>
       </c>
       <c r="R69" t="n">
-        <v>6678900</v>
+        <v>6678848</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9927,10 +9927,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125995614</v>
+        <v>125995080</v>
       </c>
       <c r="B70" t="n">
-        <v>91232</v>
+        <v>91997</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9938,34 +9938,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norsbodarna, Norsbodarna, Dlr</t>
+          <t>Norsdammen, Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492268</v>
+        <v>492347</v>
       </c>
       <c r="R70" t="n">
-        <v>6678870</v>
+        <v>6678900</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10034,32 +10034,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125995167</v>
+        <v>125995614</v>
       </c>
       <c r="B71" t="n">
-        <v>100520</v>
+        <v>91232</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492326</v>
+        <v>492268</v>
       </c>
       <c r="R71" t="n">
-        <v>6678848</v>
+        <v>6678870</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -10251,7 +10251,7 @@
         <v>125995168</v>
       </c>
       <c r="B73" t="n">
-        <v>100427</v>
+        <v>100428</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -10465,7 +10465,7 @@
         <v>125995313</v>
       </c>
       <c r="B75" t="n">
-        <v>102840</v>
+        <v>102841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -10679,7 +10679,7 @@
         <v>125995215</v>
       </c>
       <c r="B77" t="n">
-        <v>101424</v>
+        <v>101425</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9820,45 +9820,45 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125995167</v>
+        <v>125995080</v>
       </c>
       <c r="B69" t="n">
-        <v>100521</v>
+        <v>91999</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>366</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norsbodarna, Norsbodarna, Dlr</t>
+          <t>Norsdammen, Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492326</v>
+        <v>492347</v>
       </c>
       <c r="R69" t="n">
-        <v>6678848</v>
+        <v>6678900</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9927,10 +9927,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125995080</v>
+        <v>125995614</v>
       </c>
       <c r="B70" t="n">
-        <v>91997</v>
+        <v>91234</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9938,34 +9938,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Norsdammen, Norsdammen, Dlr</t>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492347</v>
+        <v>492268</v>
       </c>
       <c r="R70" t="n">
-        <v>6678900</v>
+        <v>6678870</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10034,32 +10034,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125995614</v>
+        <v>125995167</v>
       </c>
       <c r="B71" t="n">
-        <v>91232</v>
+        <v>100523</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10069,10 +10069,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>492268</v>
+        <v>492326</v>
       </c>
       <c r="R71" t="n">
-        <v>6678870</v>
+        <v>6678848</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -10144,7 +10144,7 @@
         <v>125995373</v>
       </c>
       <c r="B72" t="n">
-        <v>91285</v>
+        <v>91287</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>125995168</v>
       </c>
       <c r="B73" t="n">
-        <v>100428</v>
+        <v>100430</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
         <v>125995636</v>
       </c>
       <c r="B74" t="n">
-        <v>91246</v>
+        <v>91248</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -10465,7 +10465,7 @@
         <v>125995313</v>
       </c>
       <c r="B75" t="n">
-        <v>102841</v>
+        <v>102843</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10572,7 +10572,7 @@
         <v>125995622</v>
       </c>
       <c r="B76" t="n">
-        <v>91590</v>
+        <v>91592</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
@@ -10679,7 +10679,7 @@
         <v>125995215</v>
       </c>
       <c r="B77" t="n">
-        <v>101425</v>
+        <v>101427</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10786,7 +10786,7 @@
         <v>125995418</v>
       </c>
       <c r="B78" t="n">
-        <v>79979</v>
+        <v>79980</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10141,10 +10141,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125995373</v>
+        <v>125995168</v>
       </c>
       <c r="B72" t="n">
-        <v>91287</v>
+        <v>100430</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10152,21 +10152,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5321</v>
+        <v>222771</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10241,17 +10241,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125995168</v>
+        <v>125995373</v>
       </c>
       <c r="B73" t="n">
-        <v>100430</v>
+        <v>91287</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10259,21 +10259,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222771</v>
+        <v>5321</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9823,7 +9823,7 @@
         <v>125995080</v>
       </c>
       <c r="B69" t="n">
-        <v>91999</v>
+        <v>92001</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9930,7 +9930,7 @@
         <v>125995614</v>
       </c>
       <c r="B70" t="n">
-        <v>91234</v>
+        <v>91236</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>125995167</v>
       </c>
       <c r="B71" t="n">
-        <v>100523</v>
+        <v>100525</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -10144,7 +10144,7 @@
         <v>125995168</v>
       </c>
       <c r="B72" t="n">
-        <v>100430</v>
+        <v>100432</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10241,7 +10241,7 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -10251,7 +10251,7 @@
         <v>125995373</v>
       </c>
       <c r="B73" t="n">
-        <v>91287</v>
+        <v>91289</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
@@ -10358,7 +10358,7 @@
         <v>125995636</v>
       </c>
       <c r="B74" t="n">
-        <v>91248</v>
+        <v>91250</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10465,7 +10465,7 @@
         <v>125995313</v>
       </c>
       <c r="B75" t="n">
-        <v>102843</v>
+        <v>102845</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10562,7 +10562,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -10572,7 +10572,7 @@
         <v>125995622</v>
       </c>
       <c r="B76" t="n">
-        <v>91592</v>
+        <v>91594</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10679,7 +10679,7 @@
         <v>125995215</v>
       </c>
       <c r="B77" t="n">
-        <v>101427</v>
+        <v>101429</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10873,7 +10873,7 @@
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10141,10 +10141,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125995168</v>
+        <v>125995373</v>
       </c>
       <c r="B72" t="n">
-        <v>100432</v>
+        <v>91289</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10152,21 +10152,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222771</v>
+        <v>5321</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10241,17 +10241,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125995373</v>
+        <v>125995168</v>
       </c>
       <c r="B73" t="n">
-        <v>91289</v>
+        <v>100432</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10259,21 +10259,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5321</v>
+        <v>222771</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10348,7 +10348,7 @@
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9820,10 +9820,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125995080</v>
+        <v>125995614</v>
       </c>
       <c r="B69" t="n">
-        <v>92001</v>
+        <v>91238</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9831,34 +9831,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>366</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Norsdammen, Norsdammen, Dlr</t>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492347</v>
+        <v>492268</v>
       </c>
       <c r="R69" t="n">
-        <v>6678900</v>
+        <v>6678870</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9920,39 +9920,39 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125995614</v>
+        <v>125995167</v>
       </c>
       <c r="B70" t="n">
-        <v>91236</v>
+        <v>100527</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9962,10 +9962,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492268</v>
+        <v>492326</v>
       </c>
       <c r="R70" t="n">
-        <v>6678870</v>
+        <v>6678848</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10034,10 +10034,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>125995167</v>
+        <v>125995168</v>
       </c>
       <c r="B71" t="n">
-        <v>100525</v>
+        <v>100434</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10045,21 +10045,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222498</v>
+        <v>222771</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Svart trolldruva</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Actaea spicata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -10141,10 +10141,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>125995373</v>
+        <v>125995313</v>
       </c>
       <c r="B72" t="n">
-        <v>91289</v>
+        <v>102849</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10152,21 +10152,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5321</v>
+        <v>222002</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Barkticka</t>
+          <t>Underviol</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Oxyporus corticola</t>
+          <t>Viola mirabilis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Ryvarden</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -10241,17 +10241,17 @@
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>125995168</v>
+        <v>125995215</v>
       </c>
       <c r="B73" t="n">
-        <v>100432</v>
+        <v>101431</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10259,21 +10259,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222771</v>
+        <v>221235</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Vårärt</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Lathyrus vernus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Bernh.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -10355,48 +10355,48 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>125995636</v>
+        <v>125995418</v>
       </c>
       <c r="B74" t="n">
-        <v>91250</v>
+        <v>79980</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1204</v>
+        <v>6456</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Norsbodarna, Norsbodarna, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>492266</v>
+        <v>492332</v>
       </c>
       <c r="R74" t="n">
-        <v>6678873</v>
+        <v>6678856</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -10423,19 +10423,9 @@
           <t>2025-06-16</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>14:24</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>14:24</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -10450,7 +10440,7 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Anton Björk</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
@@ -10462,45 +10452,45 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>125995313</v>
+        <v>125995080</v>
       </c>
       <c r="B75" t="n">
-        <v>102845</v>
+        <v>92003</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222002</v>
+        <v>366</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Underviol</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Viola mirabilis</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Norsbodarna, Norsbodarna, Dlr</t>
+          <t>Norsdammen, Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>492326</v>
+        <v>492347</v>
       </c>
       <c r="R75" t="n">
-        <v>6678848</v>
+        <v>6678900</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -10562,39 +10552,39 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>125995622</v>
+        <v>125995373</v>
       </c>
       <c r="B76" t="n">
-        <v>91594</v>
+        <v>91291</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2062</v>
+        <v>5321</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Barkticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Oxyporus corticola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Fr.) Ryvarden</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -10604,10 +10594,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>492268</v>
+        <v>492326</v>
       </c>
       <c r="R76" t="n">
-        <v>6678870</v>
+        <v>6678848</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -10676,32 +10666,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>125995215</v>
+        <v>125995636</v>
       </c>
       <c r="B77" t="n">
-        <v>101429</v>
+        <v>91252</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>221235</v>
+        <v>1204</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Vårärt</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lathyrus vernus</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Bernh.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -10711,10 +10701,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>492326</v>
+        <v>492266</v>
       </c>
       <c r="R77" t="n">
-        <v>6678848</v>
+        <v>6678873</v>
       </c>
       <c r="S77" t="n">
         <v>15</v>
@@ -10783,48 +10773,48 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>125995418</v>
+        <v>125995622</v>
       </c>
       <c r="B78" t="n">
-        <v>79980</v>
+        <v>91596</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6456</v>
+        <v>2062</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsbodarna, Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>492332</v>
+        <v>492268</v>
       </c>
       <c r="R78" t="n">
-        <v>6678856</v>
+        <v>6678870</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -10851,9 +10841,19 @@
           <t>2025-06-16</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>14:24</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>14:24</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10868,7 +10868,7 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Anton Björk</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9823,7 +9823,7 @@
         <v>125995614</v>
       </c>
       <c r="B69" t="n">
-        <v>91238</v>
+        <v>91242</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -9920,7 +9920,7 @@
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -9930,7 +9930,7 @@
         <v>125995167</v>
       </c>
       <c r="B70" t="n">
-        <v>100527</v>
+        <v>100531</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>125995168</v>
       </c>
       <c r="B71" t="n">
-        <v>100434</v>
+        <v>100438</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>125995313</v>
       </c>
       <c r="B72" t="n">
-        <v>102849</v>
+        <v>102853</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>125995215</v>
       </c>
       <c r="B73" t="n">
-        <v>101431</v>
+        <v>101435</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>125995418</v>
       </c>
       <c r="B74" t="n">
-        <v>79980</v>
+        <v>79984</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10445,7 +10445,7 @@
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -10455,7 +10455,7 @@
         <v>125995080</v>
       </c>
       <c r="B75" t="n">
-        <v>92003</v>
+        <v>92007</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -10562,7 +10562,7 @@
         <v>125995373</v>
       </c>
       <c r="B76" t="n">
-        <v>91291</v>
+        <v>91295</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>125995636</v>
       </c>
       <c r="B77" t="n">
-        <v>91252</v>
+        <v>91256</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>125995622</v>
       </c>
       <c r="B78" t="n">
-        <v>91596</v>
+        <v>91600</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9930,7 +9930,7 @@
         <v>125995167</v>
       </c>
       <c r="B70" t="n">
-        <v>100531</v>
+        <v>100534</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -10037,7 +10037,7 @@
         <v>125995168</v>
       </c>
       <c r="B71" t="n">
-        <v>100438</v>
+        <v>100441</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10144,7 +10144,7 @@
         <v>125995313</v>
       </c>
       <c r="B72" t="n">
-        <v>102853</v>
+        <v>102856</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>125995215</v>
       </c>
       <c r="B73" t="n">
-        <v>101435</v>
+        <v>101438</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9820,32 +9820,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125995614</v>
+        <v>125995167</v>
       </c>
       <c r="B69" t="n">
-        <v>91242</v>
+        <v>100534</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9855,10 +9855,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492268</v>
+        <v>492326</v>
       </c>
       <c r="R69" t="n">
-        <v>6678870</v>
+        <v>6678848</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9927,32 +9927,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125995167</v>
+        <v>125995614</v>
       </c>
       <c r="B70" t="n">
-        <v>100534</v>
+        <v>91242</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9962,10 +9962,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492326</v>
+        <v>492268</v>
       </c>
       <c r="R70" t="n">
-        <v>6678848</v>
+        <v>6678870</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9820,32 +9820,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125995167</v>
+        <v>125995614</v>
       </c>
       <c r="B69" t="n">
-        <v>100534</v>
+        <v>91242</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9855,10 +9855,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492326</v>
+        <v>492268</v>
       </c>
       <c r="R69" t="n">
-        <v>6678848</v>
+        <v>6678870</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9927,32 +9927,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125995614</v>
+        <v>125995167</v>
       </c>
       <c r="B70" t="n">
-        <v>91242</v>
+        <v>100534</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9962,10 +9962,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492268</v>
+        <v>492326</v>
       </c>
       <c r="R70" t="n">
-        <v>6678870</v>
+        <v>6678848</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Andreas Öster, Anton Björk</t>
+          <t>Anton Björk, Andreas Öster</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -9820,32 +9820,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>125995614</v>
+        <v>125995167</v>
       </c>
       <c r="B69" t="n">
-        <v>91242</v>
+        <v>100543</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1202</v>
+        <v>222498</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -9855,10 +9855,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>492268</v>
+        <v>492326</v>
       </c>
       <c r="R69" t="n">
-        <v>6678870</v>
+        <v>6678848</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -9927,32 +9927,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>125995167</v>
+        <v>125995614</v>
       </c>
       <c r="B70" t="n">
-        <v>100534</v>
+        <v>91245</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222498</v>
+        <v>1202</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -9962,10 +9962,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>492326</v>
+        <v>492268</v>
       </c>
       <c r="R70" t="n">
-        <v>6678848</v>
+        <v>6678870</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -10027,7 +10027,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -10037,7 +10037,7 @@
         <v>125995168</v>
       </c>
       <c r="B71" t="n">
-        <v>100441</v>
+        <v>100450</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -10134,7 +10134,7 @@
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -10144,7 +10144,7 @@
         <v>125995313</v>
       </c>
       <c r="B72" t="n">
-        <v>102856</v>
+        <v>102865</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10251,7 +10251,7 @@
         <v>125995215</v>
       </c>
       <c r="B73" t="n">
-        <v>101438</v>
+        <v>101447</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -10358,7 +10358,7 @@
         <v>125995418</v>
       </c>
       <c r="B74" t="n">
-        <v>79984</v>
+        <v>79987</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -10455,7 +10455,7 @@
         <v>125995080</v>
       </c>
       <c r="B75" t="n">
-        <v>92007</v>
+        <v>92010</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -10552,7 +10552,7 @@
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Anton Björk, Andreas Öster</t>
+          <t>Andreas Öster, Anton Björk</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -10562,7 +10562,7 @@
         <v>125995373</v>
       </c>
       <c r="B76" t="n">
-        <v>91295</v>
+        <v>91298</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>125995636</v>
       </c>
       <c r="B77" t="n">
-        <v>91256</v>
+        <v>91259</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -10776,7 +10776,7 @@
         <v>125995622</v>
       </c>
       <c r="B78" t="n">
-        <v>91600</v>
+        <v>91603</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY78"/>
+  <dimension ref="A1:AY90"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -10878,6 +10878,1287 @@
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>127477261</v>
+      </c>
+      <c r="B79" t="n">
+        <v>98466</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>492334</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6678792</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>127478055</v>
+      </c>
+      <c r="B80" t="n">
+        <v>92644</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J80" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>492315</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6678791</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>127478884</v>
+      </c>
+      <c r="B81" t="n">
+        <v>91691</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>233025</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Skeletocutis jelicii</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Tortič &amp; A.David</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="J81" t="inlineStr"/>
+      <c r="K81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Norsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>492217</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6678944</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ81" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO81" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>127477334</v>
+      </c>
+      <c r="B82" t="n">
+        <v>90803</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>720</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J82" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>492314</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6678819</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>127476201</v>
+      </c>
+      <c r="B83" t="n">
+        <v>91326</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>492363</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6678873</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ83" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO83" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>127476197</v>
+      </c>
+      <c r="B84" t="n">
+        <v>92091</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>366</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Kandelabersvamp</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Artomyces pyxidatus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Pers.) Jülich</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="J84" t="inlineStr"/>
+      <c r="K84" t="inlineStr"/>
+      <c r="N84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>492363</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6678873</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>127476890</v>
+      </c>
+      <c r="B85" t="n">
+        <v>90856</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>256756</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Blek fingersvamp</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Ramaria pallida</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Schaeff.) Ricken</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>492320</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6678828</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>127477436</v>
+      </c>
+      <c r="B86" t="n">
+        <v>92616</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>492374</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6678752</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>127477516</v>
+      </c>
+      <c r="B87" t="n">
+        <v>79014</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>492374</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6678704</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>127478026</v>
+      </c>
+      <c r="B88" t="n">
+        <v>90803</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>720</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>492320</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6678828</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>127476668</v>
+      </c>
+      <c r="B89" t="n">
+        <v>90871</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>5754</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Gultoppig fingersvamp</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Ramaria testaceoflava</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>492311</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6678842</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>127477384</v>
+      </c>
+      <c r="B90" t="n">
+        <v>90803</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>720</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Violgubbe</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Gomphus clavatus</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>492352</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6678811</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11194,54 +11194,45 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127477334</v>
+        <v>127476201</v>
       </c>
       <c r="B82" t="n">
-        <v>90803</v>
+        <v>91326</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>720</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J82" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>492314</v>
+        <v>492363</v>
       </c>
       <c r="R82" t="n">
-        <v>6678819</v>
+        <v>6678873</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -11284,6 +11275,21 @@
       </c>
       <c r="AG82" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ82" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO82" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
@@ -11300,10 +11306,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127476201</v>
+        <v>127476197</v>
       </c>
       <c r="B83" t="n">
-        <v>91326</v>
+        <v>92091</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11311,24 +11317,27 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
+      <c r="J83" t="inlineStr"/>
+      <c r="K83" t="inlineStr"/>
+      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
@@ -11379,22 +11388,23 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
+      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
       </c>
       <c r="AJ83" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO83" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -11412,48 +11422,45 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127476197</v>
+        <v>127477436</v>
       </c>
       <c r="B84" t="n">
-        <v>92091</v>
+        <v>92616</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>366</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
-      <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>492363</v>
+        <v>492374</v>
       </c>
       <c r="R84" t="n">
-        <v>6678873</v>
+        <v>6678752</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11494,24 +11501,8 @@
       <c r="AE84" t="b">
         <v>0</v>
       </c>
-      <c r="AF84" t="inlineStr"/>
       <c r="AG84" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ84" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK84" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO84" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -11528,10 +11519,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127476890</v>
+        <v>127477516</v>
       </c>
       <c r="B85" t="n">
-        <v>90856</v>
+        <v>79014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11539,43 +11530,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>256756</v>
+        <v>6425</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Blek fingersvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramaria pallida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Schaeff.) Ricken</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492320</v>
+        <v>492374</v>
       </c>
       <c r="R85" t="n">
-        <v>6678828</v>
+        <v>6678704</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11618,6 +11600,21 @@
       </c>
       <c r="AG85" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ85" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO85" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -11634,45 +11631,54 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127477436</v>
+        <v>127476668</v>
       </c>
       <c r="B86" t="n">
-        <v>92616</v>
+        <v>90871</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>5754</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492374</v>
+        <v>492311</v>
       </c>
       <c r="R86" t="n">
-        <v>6678752</v>
+        <v>6678842</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11731,45 +11737,56 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127477516</v>
+        <v>127477334</v>
       </c>
       <c r="B87" t="n">
-        <v>79014</v>
+        <v>90803</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>720</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr"/>
+      <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492374</v>
+        <v>492314</v>
       </c>
       <c r="R87" t="n">
-        <v>6678704</v>
+        <v>6678819</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11804,29 +11821,20 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
       <c r="AE87" t="b">
         <v>0</v>
       </c>
+      <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ87" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO87" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
@@ -11843,37 +11851,37 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>127478026</v>
+        <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90803</v>
+        <v>90856</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>720</v>
+        <v>256756</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Blek fingersvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Ramaria pallida</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
+          <t>(Schaeff.) Ricken</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -11881,6 +11889,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
@@ -11925,12 +11935,18 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -11949,37 +11965,37 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>127476668</v>
+        <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90871</v>
+        <v>90803</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5754</v>
+        <v>720</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
+          <t>(Pers.) Gray</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -11987,16 +12003,18 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>492311</v>
+        <v>492320</v>
       </c>
       <c r="R89" t="n">
-        <v>6678842</v>
+        <v>6678828</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -12031,12 +12049,18 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
+      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -12093,6 +12117,8 @@
           <t>fruktkroppar</t>
         </is>
       </c>
+      <c r="K90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
@@ -12137,12 +12163,18 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
       <c r="AE90" t="b">
         <v>0</v>
       </c>
+      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
       </c>
@@ -12158,6 +12190,122 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>127502549</v>
+      </c>
+      <c r="B91" t="n">
+        <v>91291</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
+      <c r="K91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Norsådammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>492243</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6678891</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-08-14</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF91" t="inlineStr"/>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10883,7 +10883,7 @@
         <v>127477261</v>
       </c>
       <c r="B79" t="n">
-        <v>98466</v>
+        <v>98470</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>127478055</v>
       </c>
       <c r="B80" t="n">
-        <v>92644</v>
+        <v>92648</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>127478884</v>
       </c>
       <c r="B81" t="n">
-        <v>91691</v>
+        <v>91695</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>127476201</v>
       </c>
       <c r="B82" t="n">
-        <v>91326</v>
+        <v>91330</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>127476197</v>
       </c>
       <c r="B83" t="n">
-        <v>92091</v>
+        <v>92095</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>127477436</v>
       </c>
       <c r="B84" t="n">
-        <v>92616</v>
+        <v>92620</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>127477516</v>
       </c>
       <c r="B85" t="n">
-        <v>79014</v>
+        <v>79018</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>127476668</v>
       </c>
       <c r="B86" t="n">
-        <v>90871</v>
+        <v>90875</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>127477334</v>
       </c>
       <c r="B87" t="n">
-        <v>90803</v>
+        <v>90807</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90856</v>
+        <v>90860</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90803</v>
+        <v>90807</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12079,56 +12079,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127477384</v>
+        <v>127502549</v>
       </c>
       <c r="B90" t="n">
-        <v>90803</v>
+        <v>91295</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>720</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492352</v>
+        <v>492243</v>
       </c>
       <c r="R90" t="n">
-        <v>6678811</v>
+        <v>6678891</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12163,11 +12155,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Känt mycel.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12177,6 +12164,21 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12193,48 +12195,56 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127502549</v>
+        <v>127477384</v>
       </c>
       <c r="B91" t="n">
-        <v>91291</v>
+        <v>90807</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>720</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492243</v>
+        <v>492352</v>
       </c>
       <c r="R91" t="n">
-        <v>6678891</v>
+        <v>6678811</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12269,6 +12279,11 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12278,21 +12293,6 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10883,7 +10883,7 @@
         <v>127477261</v>
       </c>
       <c r="B79" t="n">
-        <v>98470</v>
+        <v>98471</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -12079,48 +12079,56 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127502549</v>
+        <v>127477384</v>
       </c>
       <c r="B90" t="n">
-        <v>91295</v>
+        <v>90807</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>720</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492243</v>
+        <v>492352</v>
       </c>
       <c r="R90" t="n">
-        <v>6678891</v>
+        <v>6678811</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12155,6 +12163,11 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12164,21 +12177,6 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12195,56 +12193,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127477384</v>
+        <v>127502549</v>
       </c>
       <c r="B91" t="n">
-        <v>90807</v>
+        <v>91295</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>720</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492352</v>
+        <v>492243</v>
       </c>
       <c r="R91" t="n">
-        <v>6678811</v>
+        <v>6678891</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12279,11 +12269,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Känt mycel.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12293,6 +12278,21 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12079,56 +12079,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127477384</v>
+        <v>127502549</v>
       </c>
       <c r="B90" t="n">
-        <v>90807</v>
+        <v>91295</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>720</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492352</v>
+        <v>492243</v>
       </c>
       <c r="R90" t="n">
-        <v>6678811</v>
+        <v>6678891</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12163,11 +12155,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Känt mycel.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12177,6 +12164,21 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12193,48 +12195,56 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127502549</v>
+        <v>127477384</v>
       </c>
       <c r="B91" t="n">
-        <v>91295</v>
+        <v>90807</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>720</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492243</v>
+        <v>492352</v>
       </c>
       <c r="R91" t="n">
-        <v>6678891</v>
+        <v>6678811</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12269,6 +12279,11 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12278,21 +12293,6 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10883,7 +10883,7 @@
         <v>127477261</v>
       </c>
       <c r="B79" t="n">
-        <v>98471</v>
+        <v>98473</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>127478055</v>
       </c>
       <c r="B80" t="n">
-        <v>92648</v>
+        <v>92650</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>127478884</v>
       </c>
       <c r="B81" t="n">
-        <v>91695</v>
+        <v>91697</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>127476201</v>
       </c>
       <c r="B82" t="n">
-        <v>91330</v>
+        <v>91332</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>127476197</v>
       </c>
       <c r="B83" t="n">
-        <v>92095</v>
+        <v>92097</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>127477436</v>
       </c>
       <c r="B84" t="n">
-        <v>92620</v>
+        <v>92622</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>127477516</v>
       </c>
       <c r="B85" t="n">
-        <v>79018</v>
+        <v>79020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>127476668</v>
       </c>
       <c r="B86" t="n">
-        <v>90875</v>
+        <v>90877</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>127477334</v>
       </c>
       <c r="B87" t="n">
-        <v>90807</v>
+        <v>90809</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90860</v>
+        <v>90862</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90807</v>
+        <v>90809</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12079,48 +12079,56 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127502549</v>
+        <v>127477384</v>
       </c>
       <c r="B90" t="n">
-        <v>91295</v>
+        <v>90809</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>720</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492243</v>
+        <v>492352</v>
       </c>
       <c r="R90" t="n">
-        <v>6678891</v>
+        <v>6678811</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12155,6 +12163,11 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12164,21 +12177,6 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12195,56 +12193,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127477384</v>
+        <v>127502549</v>
       </c>
       <c r="B91" t="n">
-        <v>90807</v>
+        <v>91297</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>720</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492352</v>
+        <v>492243</v>
       </c>
       <c r="R91" t="n">
-        <v>6678811</v>
+        <v>6678891</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12279,11 +12269,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Känt mycel.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12293,6 +12278,21 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12079,56 +12079,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127477384</v>
+        <v>127502549</v>
       </c>
       <c r="B90" t="n">
-        <v>90809</v>
+        <v>91297</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>720</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492352</v>
+        <v>492243</v>
       </c>
       <c r="R90" t="n">
-        <v>6678811</v>
+        <v>6678891</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12163,11 +12155,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Känt mycel.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12177,6 +12164,21 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12193,48 +12195,56 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127502549</v>
+        <v>127477384</v>
       </c>
       <c r="B91" t="n">
-        <v>91297</v>
+        <v>90809</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>720</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492243</v>
+        <v>492352</v>
       </c>
       <c r="R91" t="n">
-        <v>6678891</v>
+        <v>6678811</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12269,6 +12279,11 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12278,21 +12293,6 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10883,7 +10883,7 @@
         <v>127477261</v>
       </c>
       <c r="B79" t="n">
-        <v>98473</v>
+        <v>98479</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>127478055</v>
       </c>
       <c r="B80" t="n">
-        <v>92650</v>
+        <v>92656</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>127478884</v>
       </c>
       <c r="B81" t="n">
-        <v>91697</v>
+        <v>91703</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>127476201</v>
       </c>
       <c r="B82" t="n">
-        <v>91332</v>
+        <v>91338</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>127476197</v>
       </c>
       <c r="B83" t="n">
-        <v>92097</v>
+        <v>92103</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>127477436</v>
       </c>
       <c r="B84" t="n">
-        <v>92622</v>
+        <v>92628</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>127476668</v>
       </c>
       <c r="B86" t="n">
-        <v>90877</v>
+        <v>90883</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>127477334</v>
       </c>
       <c r="B87" t="n">
-        <v>90809</v>
+        <v>90815</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90862</v>
+        <v>90868</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90809</v>
+        <v>90815</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12079,48 +12079,56 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127502549</v>
+        <v>127477384</v>
       </c>
       <c r="B90" t="n">
-        <v>91297</v>
+        <v>90815</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>720</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492243</v>
+        <v>492352</v>
       </c>
       <c r="R90" t="n">
-        <v>6678891</v>
+        <v>6678811</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12155,6 +12163,11 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12164,21 +12177,6 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12195,56 +12193,48 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127477384</v>
+        <v>127502549</v>
       </c>
       <c r="B91" t="n">
-        <v>90809</v>
+        <v>91303</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>720</v>
+        <v>5447</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492352</v>
+        <v>492243</v>
       </c>
       <c r="R91" t="n">
-        <v>6678811</v>
+        <v>6678891</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12279,11 +12269,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Känt mycel.</t>
-        </is>
-      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12293,6 +12278,21 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10883,7 +10883,7 @@
         <v>127477261</v>
       </c>
       <c r="B79" t="n">
-        <v>98479</v>
+        <v>98482</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>127478055</v>
       </c>
       <c r="B80" t="n">
-        <v>92656</v>
+        <v>92659</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>127478884</v>
       </c>
       <c r="B81" t="n">
-        <v>91703</v>
+        <v>91706</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>127476201</v>
       </c>
       <c r="B82" t="n">
-        <v>91338</v>
+        <v>91341</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>127476197</v>
       </c>
       <c r="B83" t="n">
-        <v>92103</v>
+        <v>92106</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>127477436</v>
       </c>
       <c r="B84" t="n">
-        <v>92628</v>
+        <v>92631</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>127477516</v>
       </c>
       <c r="B85" t="n">
-        <v>79020</v>
+        <v>79023</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>127476668</v>
       </c>
       <c r="B86" t="n">
-        <v>90883</v>
+        <v>90886</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>127477334</v>
       </c>
       <c r="B87" t="n">
-        <v>90815</v>
+        <v>90818</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90868</v>
+        <v>90871</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90815</v>
+        <v>90818</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12082,7 +12082,7 @@
         <v>127477384</v>
       </c>
       <c r="B90" t="n">
-        <v>90815</v>
+        <v>90818</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12196,7 +12196,7 @@
         <v>127502549</v>
       </c>
       <c r="B91" t="n">
-        <v>91303</v>
+        <v>91306</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10883,7 +10883,7 @@
         <v>127477261</v>
       </c>
       <c r="B79" t="n">
-        <v>98482</v>
+        <v>98490</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>127478055</v>
       </c>
       <c r="B80" t="n">
-        <v>92659</v>
+        <v>92667</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>127478884</v>
       </c>
       <c r="B81" t="n">
-        <v>91706</v>
+        <v>91714</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11197,7 +11197,7 @@
         <v>127476201</v>
       </c>
       <c r="B82" t="n">
-        <v>91341</v>
+        <v>91349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11309,7 +11309,7 @@
         <v>127476197</v>
       </c>
       <c r="B83" t="n">
-        <v>92106</v>
+        <v>92114</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11425,7 +11425,7 @@
         <v>127477436</v>
       </c>
       <c r="B84" t="n">
-        <v>92631</v>
+        <v>92639</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -11522,7 +11522,7 @@
         <v>127477516</v>
       </c>
       <c r="B85" t="n">
-        <v>79023</v>
+        <v>79029</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11634,7 +11634,7 @@
         <v>127476668</v>
       </c>
       <c r="B86" t="n">
-        <v>90886</v>
+        <v>90894</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11740,7 +11740,7 @@
         <v>127477334</v>
       </c>
       <c r="B87" t="n">
-        <v>90818</v>
+        <v>90826</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11854,7 +11854,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90871</v>
+        <v>90879</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11968,7 +11968,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90818</v>
+        <v>90826</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12079,56 +12079,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127477384</v>
+        <v>127502549</v>
       </c>
       <c r="B90" t="n">
-        <v>90818</v>
+        <v>91314</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>720</v>
+        <v>5447</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
       <c r="K90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492352</v>
+        <v>492243</v>
       </c>
       <c r="R90" t="n">
-        <v>6678811</v>
+        <v>6678891</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12163,11 +12155,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Känt mycel.</t>
-        </is>
-      </c>
       <c r="AD90" t="b">
         <v>0</v>
       </c>
@@ -12177,6 +12164,21 @@
       <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12193,48 +12195,56 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127502549</v>
+        <v>127477384</v>
       </c>
       <c r="B91" t="n">
-        <v>91306</v>
+        <v>90826</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5447</v>
+        <v>720</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
-      <c r="J91" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492243</v>
+        <v>492352</v>
       </c>
       <c r="R91" t="n">
-        <v>6678891</v>
+        <v>6678811</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12269,6 +12279,11 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD91" t="b">
         <v>0</v>
       </c>
@@ -12278,21 +12293,6 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ91" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO91" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10883,7 +10883,7 @@
         <v>127477261</v>
       </c>
       <c r="B79" t="n">
-        <v>98490</v>
+        <v>98491</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>127478055</v>
       </c>
       <c r="B80" t="n">
-        <v>92667</v>
+        <v>92668</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11083,43 +11083,45 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>127478884</v>
+        <v>127476201</v>
       </c>
       <c r="B81" t="n">
-        <v>91714</v>
+        <v>91350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>233025</v>
+        <v>1202</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Skeletocutis jelicii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Tortič &amp; A.David</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="J81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
-      <c r="N81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>492217</v>
+        <v>492363</v>
       </c>
       <c r="R81" t="n">
-        <v>6678944</v>
+        <v>6678873</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -11160,7 +11162,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -11194,10 +11195,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>127476201</v>
+        <v>127476197</v>
       </c>
       <c r="B82" t="n">
-        <v>91349</v>
+        <v>92115</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11205,24 +11206,27 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>366</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Kandelabersvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Artomyces pyxidatus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Pers.) Jülich</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
+      <c r="J82" t="inlineStr"/>
+      <c r="K82" t="inlineStr"/>
+      <c r="N82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
@@ -11273,22 +11277,23 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
       <c r="AJ82" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK82" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO82" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -11306,48 +11311,45 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>127476197</v>
+        <v>127477436</v>
       </c>
       <c r="B83" t="n">
-        <v>92114</v>
+        <v>92640</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>366</v>
+        <v>4364</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kandelabersvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Artomyces pyxidatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Pers.) Jülich</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
-      <c r="J83" t="inlineStr"/>
-      <c r="K83" t="inlineStr"/>
-      <c r="N83" t="inlineStr"/>
       <c r="P83" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>492363</v>
+        <v>492374</v>
       </c>
       <c r="R83" t="n">
-        <v>6678873</v>
+        <v>6678752</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -11388,24 +11390,8 @@
       <c r="AE83" t="b">
         <v>0</v>
       </c>
-      <c r="AF83" t="inlineStr"/>
       <c r="AG83" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ83" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK83" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO83" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
@@ -11422,32 +11408,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>127477436</v>
+        <v>127477516</v>
       </c>
       <c r="B84" t="n">
-        <v>92639</v>
+        <v>79029</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -11460,7 +11446,7 @@
         <v>492374</v>
       </c>
       <c r="R84" t="n">
-        <v>6678752</v>
+        <v>6678704</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -11503,6 +11489,21 @@
       </c>
       <c r="AG84" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ84" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO84" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
@@ -11519,45 +11520,56 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>127477516</v>
+        <v>127477334</v>
       </c>
       <c r="B85" t="n">
-        <v>79029</v>
+        <v>90827</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6425</v>
+        <v>720</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>492374</v>
+        <v>492314</v>
       </c>
       <c r="R85" t="n">
-        <v>6678704</v>
+        <v>6678819</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -11592,29 +11604,20 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
       <c r="AE85" t="b">
         <v>0</v>
       </c>
+      <c r="AF85" t="inlineStr"/>
       <c r="AG85" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ85" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO85" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
@@ -11631,54 +11634,48 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127476668</v>
+        <v>127502549</v>
       </c>
       <c r="B86" t="n">
-        <v>90894</v>
+        <v>91315</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5754</v>
+        <v>5447</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gultoppig fingersvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramaria testaceoflava</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Bres.) Corner</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr"/>
+      <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492311</v>
+        <v>492243</v>
       </c>
       <c r="R86" t="n">
-        <v>6678842</v>
+        <v>6678891</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11719,8 +11716,24 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
+      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ86" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO86" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -11737,10 +11750,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127477334</v>
+        <v>127477384</v>
       </c>
       <c r="B87" t="n">
-        <v>90826</v>
+        <v>90827</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11767,7 +11780,7 @@
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>9</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -11783,10 +11796,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492314</v>
+        <v>492352</v>
       </c>
       <c r="R87" t="n">
-        <v>6678819</v>
+        <v>6678811</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11854,7 +11867,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90879</v>
+        <v>90880</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11968,7 +11981,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90826</v>
+        <v>90827</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12079,48 +12092,54 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>127502549</v>
+        <v>127476668</v>
       </c>
       <c r="B90" t="n">
-        <v>91314</v>
+        <v>90895</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>5447</v>
+        <v>5754</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gultoppig fingersvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Ramaria testaceoflava</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+          <t>(Bres.) Corner</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="J90" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>492243</v>
+        <v>492311</v>
       </c>
       <c r="R90" t="n">
-        <v>6678891</v>
+        <v>6678842</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -12161,24 +12180,8 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO90" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
@@ -12195,56 +12198,43 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>127477384</v>
+        <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>90826</v>
+        <v>91715</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>720</v>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>Violgubbe</t>
-        </is>
+        <v>233025</v>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Skeletocutis jelicii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J91" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Tortič &amp; A.David</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="J91" t="inlineStr"/>
       <c r="K91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>492352</v>
+        <v>492217</v>
       </c>
       <c r="R91" t="n">
-        <v>6678811</v>
+        <v>6678944</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -12281,7 +12271,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Känt mycel.</t>
+          <t>Väntar på mikroskopering.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12293,6 +12283,21 @@
       <c r="AF91" t="inlineStr"/>
       <c r="AG91" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ91" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO91" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10883,7 +10883,7 @@
         <v>127477261</v>
       </c>
       <c r="B79" t="n">
-        <v>98491</v>
+        <v>98492</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>127478055</v>
       </c>
       <c r="B80" t="n">
-        <v>92668</v>
+        <v>92669</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>127476201</v>
       </c>
       <c r="B81" t="n">
-        <v>91350</v>
+        <v>91351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>127476197</v>
       </c>
       <c r="B82" t="n">
-        <v>92115</v>
+        <v>92116</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>127477436</v>
       </c>
       <c r="B83" t="n">
-        <v>92640</v>
+        <v>92641</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>127477334</v>
       </c>
       <c r="B85" t="n">
-        <v>90827</v>
+        <v>90828</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>127502549</v>
       </c>
       <c r="B86" t="n">
-        <v>91315</v>
+        <v>91316</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>127477384</v>
       </c>
       <c r="B87" t="n">
-        <v>90827</v>
+        <v>90828</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90880</v>
+        <v>90881</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90827</v>
+        <v>90828</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>127476668</v>
       </c>
       <c r="B90" t="n">
-        <v>90895</v>
+        <v>90896</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91715</v>
+        <v>91716</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -10883,7 +10883,7 @@
         <v>127477261</v>
       </c>
       <c r="B79" t="n">
-        <v>98492</v>
+        <v>98493</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -10980,7 +10980,7 @@
         <v>127478055</v>
       </c>
       <c r="B80" t="n">
-        <v>92669</v>
+        <v>92670</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -11086,7 +11086,7 @@
         <v>127476201</v>
       </c>
       <c r="B81" t="n">
-        <v>91351</v>
+        <v>91352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -11198,7 +11198,7 @@
         <v>127476197</v>
       </c>
       <c r="B82" t="n">
-        <v>92116</v>
+        <v>92117</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -11314,7 +11314,7 @@
         <v>127477436</v>
       </c>
       <c r="B83" t="n">
-        <v>92641</v>
+        <v>92642</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -11523,7 +11523,7 @@
         <v>127477334</v>
       </c>
       <c r="B85" t="n">
-        <v>90828</v>
+        <v>90829</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -11637,7 +11637,7 @@
         <v>127502549</v>
       </c>
       <c r="B86" t="n">
-        <v>91316</v>
+        <v>91317</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -11753,7 +11753,7 @@
         <v>127477384</v>
       </c>
       <c r="B87" t="n">
-        <v>90828</v>
+        <v>90829</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -11867,7 +11867,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90881</v>
+        <v>90882</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90828</v>
+        <v>90829</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>127476668</v>
       </c>
       <c r="B90" t="n">
-        <v>90896</v>
+        <v>90897</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91716</v>
+        <v>91717</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -11634,48 +11634,56 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>127502549</v>
+        <v>127477384</v>
       </c>
       <c r="B86" t="n">
-        <v>91317</v>
+        <v>90829</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>5447</v>
+        <v>720</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Violgubbe</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Gomphus clavatus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
+          <t>(Pers.) Gray</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="P86" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>492243</v>
+        <v>492352</v>
       </c>
       <c r="R86" t="n">
-        <v>6678891</v>
+        <v>6678811</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -11710,6 +11718,11 @@
           <t>2025-08-14</t>
         </is>
       </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Känt mycel.</t>
+        </is>
+      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -11719,21 +11732,6 @@
       <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO86" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
@@ -11750,56 +11748,48 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>127477384</v>
+        <v>127502549</v>
       </c>
       <c r="B87" t="n">
-        <v>90829</v>
+        <v>91317</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>720</v>
+        <v>5447</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Violgubbe</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Gomphus clavatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Pers.) Gray</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="J87" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="J87" t="inlineStr"/>
       <c r="K87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>492352</v>
+        <v>492243</v>
       </c>
       <c r="R87" t="n">
-        <v>6678811</v>
+        <v>6678891</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -11834,11 +11824,6 @@
           <t>2025-08-14</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Känt mycel.</t>
-        </is>
-      </c>
       <c r="AD87" t="b">
         <v>0</v>
       </c>
@@ -11848,6 +11833,21 @@
       <c r="AF87" t="inlineStr"/>
       <c r="AG87" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO87" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -11867,7 +11867,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90882</v>
+        <v>90888</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90829</v>
+        <v>90835</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>127476668</v>
       </c>
       <c r="B90" t="n">
-        <v>90897</v>
+        <v>90903</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91717</v>
+        <v>91725</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -11867,7 +11867,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90888</v>
+        <v>90980</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90835</v>
+        <v>90927</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>127476668</v>
       </c>
       <c r="B90" t="n">
-        <v>90903</v>
+        <v>90995</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91725</v>
+        <v>91817</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -11867,7 +11867,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90980</v>
+        <v>90992</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90927</v>
+        <v>90939</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>127476668</v>
       </c>
       <c r="B90" t="n">
-        <v>90995</v>
+        <v>91007</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91817</v>
+        <v>91829</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -11867,7 +11867,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90992</v>
+        <v>90994</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90939</v>
+        <v>90941</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>127476668</v>
       </c>
       <c r="B90" t="n">
-        <v>91007</v>
+        <v>91009</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91829</v>
+        <v>91831</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY91"/>
+  <dimension ref="A1:AY107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11867,7 +11867,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90994</v>
+        <v>90995</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90941</v>
+        <v>90942</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>127476668</v>
       </c>
       <c r="B90" t="n">
-        <v>91009</v>
+        <v>91010</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91831</v>
+        <v>91832</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12312,6 +12312,1655 @@
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>128803366</v>
+      </c>
+      <c r="B92" t="n">
+        <v>92785</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>5449</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Phellodon niger</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Norsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>492306</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6678952</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>128802766</v>
+      </c>
+      <c r="B93" t="n">
+        <v>90849</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Norsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>492251</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6678983</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>128804210</v>
+      </c>
+      <c r="B94" t="n">
+        <v>90849</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>5685</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Gullgröppa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Pseudomerulius aureus</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>(Fr.) Jülich</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Norsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>492325</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6678917</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>128803336</v>
+      </c>
+      <c r="B95" t="n">
+        <v>92757</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>4364</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Dropptaggsvamp</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hydnellum ferrugineum</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Norsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>492306</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6678952</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>128805458</v>
+      </c>
+      <c r="B96" t="n">
+        <v>91877</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>4217</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Blodticka</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Meruliopsis taxicola</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Bondartsev</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Norsådammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>492302</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6678779</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF96" t="inlineStr"/>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>128804682</v>
+      </c>
+      <c r="B97" t="n">
+        <v>91679</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>1106</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Vågticka</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Osteina undosa</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>(Peck) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>492333</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6678887</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>128806459</v>
+      </c>
+      <c r="B98" t="n">
+        <v>91467</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Norsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>492279</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6678964</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>128803026</v>
+      </c>
+      <c r="B99" t="n">
+        <v>91467</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Norsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>492205</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6679020</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>128805456</v>
+      </c>
+      <c r="B100" t="n">
+        <v>92195</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>1105</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Laxporing</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Rhodonia placenta</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>Norsådammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>492302</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6678779</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>128805857</v>
+      </c>
+      <c r="B101" t="n">
+        <v>91747</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E101" t="n">
+        <v>1964</v>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>Honungsticka</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Fomitopsis mellita</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
+      <c r="P101" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q101" t="n">
+        <v>492381</v>
+      </c>
+      <c r="R101" t="n">
+        <v>6678643</v>
+      </c>
+      <c r="S101" t="n">
+        <v>10</v>
+      </c>
+      <c r="T101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG101" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT101" t="inlineStr"/>
+      <c r="AW101" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX101" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY101" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>128803412</v>
+      </c>
+      <c r="B102" t="n">
+        <v>92783</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E102" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
+      <c r="P102" t="inlineStr">
+        <is>
+          <t>Norsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q102" t="n">
+        <v>492284</v>
+      </c>
+      <c r="R102" t="n">
+        <v>6678978</v>
+      </c>
+      <c r="S102" t="n">
+        <v>10</v>
+      </c>
+      <c r="T102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U102" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V102" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W102" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y102" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA102" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG102" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT102" t="inlineStr"/>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>128805191</v>
+      </c>
+      <c r="B103" t="n">
+        <v>91921</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E103" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Phlebia centrifuga</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>P.Karst.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="P103" t="inlineStr">
+        <is>
+          <t>Norsådammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q103" t="n">
+        <v>492220</v>
+      </c>
+      <c r="R103" t="n">
+        <v>6678844</v>
+      </c>
+      <c r="S103" t="n">
+        <v>10</v>
+      </c>
+      <c r="T103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U103" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V103" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W103" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y103" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA103" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG103" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT103" t="inlineStr"/>
+      <c r="AW103" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX103" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY103" t="inlineStr"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>128805477</v>
+      </c>
+      <c r="B104" t="n">
+        <v>91873</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E104" t="n">
+        <v>6040162</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Leptoporus erubescens</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
+      <c r="P104" t="inlineStr">
+        <is>
+          <t>Norsådammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q104" t="n">
+        <v>492302</v>
+      </c>
+      <c r="R104" t="n">
+        <v>6678779</v>
+      </c>
+      <c r="S104" t="n">
+        <v>10</v>
+      </c>
+      <c r="T104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U104" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V104" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W104" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y104" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA104" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF104" t="inlineStr"/>
+      <c r="AG104" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AT104" t="inlineStr"/>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>128803288</v>
+      </c>
+      <c r="B105" t="n">
+        <v>96838</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E105" t="n">
+        <v>53</v>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Vedtrappmossa</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Crossocalyx hellerianus</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
+      <c r="P105" t="inlineStr">
+        <is>
+          <t>Norsdammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q105" t="n">
+        <v>492285</v>
+      </c>
+      <c r="R105" t="n">
+        <v>6678945</v>
+      </c>
+      <c r="S105" t="n">
+        <v>10</v>
+      </c>
+      <c r="T105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U105" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V105" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W105" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y105" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA105" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG105" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT105" t="inlineStr"/>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>128805579</v>
+      </c>
+      <c r="B106" t="n">
+        <v>80067</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E106" t="n">
+        <v>392</v>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>Aspgelélav</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>Collema subnigrescens</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>Degel.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="P106" t="inlineStr">
+        <is>
+          <t>Norsådammen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q106" t="n">
+        <v>492277</v>
+      </c>
+      <c r="R106" t="n">
+        <v>6678747</v>
+      </c>
+      <c r="S106" t="n">
+        <v>10</v>
+      </c>
+      <c r="T106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U106" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V106" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W106" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y106" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA106" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG106" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ106" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK106" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO106" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AT106" t="inlineStr"/>
+      <c r="AW106" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX106" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY106" t="inlineStr"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>128806246</v>
+      </c>
+      <c r="B107" t="n">
+        <v>86729</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E107" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
+      <c r="P107" t="inlineStr">
+        <is>
+          <t>Norsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q107" t="n">
+        <v>492325</v>
+      </c>
+      <c r="R107" t="n">
+        <v>6678794</v>
+      </c>
+      <c r="S107" t="n">
+        <v>10</v>
+      </c>
+      <c r="T107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U107" t="inlineStr">
+        <is>
+          <t>Ludvika</t>
+        </is>
+      </c>
+      <c r="V107" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W107" t="inlineStr">
+        <is>
+          <t>Grangärde</t>
+        </is>
+      </c>
+      <c r="Y107" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AA107" t="inlineStr">
+        <is>
+          <t>2025-09-30</t>
+        </is>
+      </c>
+      <c r="AD107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG107" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT107" t="inlineStr"/>
+      <c r="AW107" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AX107" t="inlineStr">
+        <is>
+          <t>Anton Björk</t>
+        </is>
+      </c>
+      <c r="AY107" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92785</v>
+        <v>92812</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90849</v>
+        <v>90876</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90849</v>
+        <v>90876</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>128803336</v>
       </c>
       <c r="B95" t="n">
-        <v>92757</v>
+        <v>92784</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12705,7 +12705,7 @@
         <v>128805458</v>
       </c>
       <c r="B96" t="n">
-        <v>91877</v>
+        <v>91904</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12818,45 +12818,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128804682</v>
+        <v>128806459</v>
       </c>
       <c r="B97" t="n">
-        <v>91679</v>
+        <v>91494</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492333</v>
+        <v>492279</v>
       </c>
       <c r="R97" t="n">
-        <v>6678887</v>
+        <v>6678964</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12899,21 +12899,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12930,45 +12915,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128806459</v>
+        <v>128804682</v>
       </c>
       <c r="B98" t="n">
-        <v>91467</v>
+        <v>91706</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492279</v>
+        <v>492333</v>
       </c>
       <c r="R98" t="n">
-        <v>6678964</v>
+        <v>6678887</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13011,6 +12996,21 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -13027,45 +13027,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128803026</v>
+        <v>128805857</v>
       </c>
       <c r="B99" t="n">
-        <v>91467</v>
+        <v>91774</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492205</v>
+        <v>492381</v>
       </c>
       <c r="R99" t="n">
-        <v>6679020</v>
+        <v>6678643</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13108,6 +13108,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13127,7 +13142,7 @@
         <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>92195</v>
+        <v>92222</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13240,45 +13255,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805857</v>
+        <v>128803026</v>
       </c>
       <c r="B101" t="n">
-        <v>91747</v>
+        <v>91494</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1964</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492381</v>
+        <v>492205</v>
       </c>
       <c r="R101" t="n">
-        <v>6678643</v>
+        <v>6679020</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13321,21 +13336,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13352,10 +13352,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128803412</v>
+        <v>128805477</v>
       </c>
       <c r="B102" t="n">
-        <v>92783</v>
+        <v>91900</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13363,34 +13363,32 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492284</v>
+        <v>492302</v>
       </c>
       <c r="R102" t="n">
-        <v>6678978</v>
+        <v>6678779</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13431,8 +13429,24 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13452,7 +13466,7 @@
         <v>128805191</v>
       </c>
       <c r="B103" t="n">
-        <v>91921</v>
+        <v>91948</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13546,10 +13560,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805477</v>
+        <v>128803412</v>
       </c>
       <c r="B104" t="n">
-        <v>91873</v>
+        <v>92810</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13557,32 +13571,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492302</v>
+        <v>492284</v>
       </c>
       <c r="R104" t="n">
-        <v>6678779</v>
+        <v>6678978</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13623,24 +13639,8 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -13660,7 +13660,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96838</v>
+        <v>96865</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>128805579</v>
       </c>
       <c r="B106" t="n">
-        <v>80067</v>
+        <v>80094</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>128806246</v>
       </c>
       <c r="B107" t="n">
-        <v>86729</v>
+        <v>86756</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -11867,7 +11867,7 @@
         <v>127476890</v>
       </c>
       <c r="B88" t="n">
-        <v>90995</v>
+        <v>91022</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -11981,7 +11981,7 @@
         <v>127478026</v>
       </c>
       <c r="B89" t="n">
-        <v>90942</v>
+        <v>90969</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -12095,7 +12095,7 @@
         <v>127476668</v>
       </c>
       <c r="B90" t="n">
-        <v>91010</v>
+        <v>91037</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91832</v>
+        <v>91859</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12605,10 +12605,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128803336</v>
+        <v>128805458</v>
       </c>
       <c r="B95" t="n">
-        <v>92784</v>
+        <v>91904</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12616,34 +12616,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492306</v>
+        <v>492302</v>
       </c>
       <c r="R95" t="n">
-        <v>6678952</v>
+        <v>6678779</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12684,8 +12687,24 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12702,10 +12721,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128805458</v>
+        <v>128803336</v>
       </c>
       <c r="B96" t="n">
-        <v>91904</v>
+        <v>92784</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12713,37 +12732,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4217</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492302</v>
+        <v>492306</v>
       </c>
       <c r="R96" t="n">
-        <v>6678779</v>
+        <v>6678952</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12784,24 +12800,8 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -13027,45 +13027,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128805857</v>
+        <v>128803026</v>
       </c>
       <c r="B99" t="n">
-        <v>91774</v>
+        <v>91494</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1964</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492381</v>
+        <v>492205</v>
       </c>
       <c r="R99" t="n">
-        <v>6678643</v>
+        <v>6679020</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13108,21 +13108,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13139,10 +13124,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B100" t="n">
-        <v>92222</v>
+        <v>91774</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13150,37 +13135,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R100" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13221,23 +13203,22 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13255,45 +13236,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128803026</v>
+        <v>128805456</v>
       </c>
       <c r="B101" t="n">
-        <v>91494</v>
+        <v>92222</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492205</v>
+        <v>492302</v>
       </c>
       <c r="R101" t="n">
-        <v>6679020</v>
+        <v>6678779</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13334,8 +13318,24 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13352,43 +13352,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805477</v>
+        <v>128805191</v>
       </c>
       <c r="B102" t="n">
-        <v>91900</v>
+        <v>91948</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6040162</v>
+        <v>1209</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492302</v>
+        <v>492220</v>
       </c>
       <c r="R102" t="n">
-        <v>6678779</v>
+        <v>6678844</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13429,24 +13431,8 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13463,45 +13449,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128805191</v>
+        <v>128803412</v>
       </c>
       <c r="B103" t="n">
-        <v>91948</v>
+        <v>92810</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
+        <v>5448</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492220</v>
+        <v>492284</v>
       </c>
       <c r="R103" t="n">
-        <v>6678844</v>
+        <v>6678978</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13560,10 +13546,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128803412</v>
+        <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>92810</v>
+        <v>91900</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13571,34 +13557,32 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492284</v>
+        <v>492302</v>
       </c>
       <c r="R104" t="n">
-        <v>6678978</v>
+        <v>6678779</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13639,8 +13623,24 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92812</v>
+        <v>92817</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12414,7 +12414,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90876</v>
+        <v>90881</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12511,7 +12511,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90876</v>
+        <v>90881</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12608,7 +12608,7 @@
         <v>128805458</v>
       </c>
       <c r="B95" t="n">
-        <v>91904</v>
+        <v>91909</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12724,7 +12724,7 @@
         <v>128803336</v>
       </c>
       <c r="B96" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12818,45 +12818,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128806459</v>
+        <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91494</v>
+        <v>91711</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492279</v>
+        <v>492333</v>
       </c>
       <c r="R97" t="n">
-        <v>6678964</v>
+        <v>6678887</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12899,6 +12899,21 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12915,45 +12930,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128804682</v>
+        <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91706</v>
+        <v>91499</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492333</v>
+        <v>492279</v>
       </c>
       <c r="R98" t="n">
-        <v>6678887</v>
+        <v>6678964</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12996,21 +13011,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -13030,7 +13030,7 @@
         <v>128803026</v>
       </c>
       <c r="B99" t="n">
-        <v>91494</v>
+        <v>91499</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13124,10 +13124,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805857</v>
+        <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>91774</v>
+        <v>92227</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13135,34 +13135,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1964</v>
+        <v>1105</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492381</v>
+        <v>492302</v>
       </c>
       <c r="R100" t="n">
-        <v>6678643</v>
+        <v>6678779</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13203,22 +13206,23 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13236,10 +13240,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>92222</v>
+        <v>91779</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13247,37 +13251,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R101" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13318,23 +13319,22 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13352,45 +13352,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805191</v>
+        <v>128803412</v>
       </c>
       <c r="B102" t="n">
-        <v>91948</v>
+        <v>92815</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1209</v>
+        <v>5448</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492220</v>
+        <v>492284</v>
       </c>
       <c r="R102" t="n">
-        <v>6678844</v>
+        <v>6678978</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13449,45 +13449,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128803412</v>
+        <v>128805191</v>
       </c>
       <c r="B103" t="n">
-        <v>92810</v>
+        <v>91953</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5448</v>
+        <v>1209</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492284</v>
+        <v>492220</v>
       </c>
       <c r="R103" t="n">
-        <v>6678978</v>
+        <v>6678844</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13549,7 +13549,7 @@
         <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>91900</v>
+        <v>91905</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13660,7 +13660,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96865</v>
+        <v>96871</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13757,7 +13757,7 @@
         <v>128805579</v>
       </c>
       <c r="B106" t="n">
-        <v>80094</v>
+        <v>80098</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13869,7 +13869,7 @@
         <v>128806246</v>
       </c>
       <c r="B107" t="n">
-        <v>86756</v>
+        <v>86760</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92817</v>
+        <v>92823</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12327,21 +12327,12 @@
       <c r="E92" t="n">
         <v>5449</v>
       </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>Svart taggsvamp</t>
-        </is>
-      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr">
-        <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
+          <t>Phellodon niger s.lat</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
       <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
@@ -12414,7 +12405,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90881</v>
+        <v>90886</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12511,7 +12502,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90881</v>
+        <v>90886</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12608,7 +12599,7 @@
         <v>128805458</v>
       </c>
       <c r="B95" t="n">
-        <v>91909</v>
+        <v>91914</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12724,7 +12715,7 @@
         <v>128803336</v>
       </c>
       <c r="B96" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12821,7 +12812,7 @@
         <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91711</v>
+        <v>91716</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12933,7 +12924,7 @@
         <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13030,7 +13021,7 @@
         <v>128803026</v>
       </c>
       <c r="B99" t="n">
-        <v>91499</v>
+        <v>91504</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13127,7 +13118,7 @@
         <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>92227</v>
+        <v>92232</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13243,7 +13234,7 @@
         <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>91779</v>
+        <v>91784</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13355,7 +13346,7 @@
         <v>128803412</v>
       </c>
       <c r="B102" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13452,7 +13443,7 @@
         <v>128805191</v>
       </c>
       <c r="B103" t="n">
-        <v>91953</v>
+        <v>91958</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13549,7 +13540,7 @@
         <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>91905</v>
+        <v>91910</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13660,7 +13651,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96871</v>
+        <v>96878</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12809,45 +12809,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128804682</v>
+        <v>128806459</v>
       </c>
       <c r="B97" t="n">
-        <v>91716</v>
+        <v>91504</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492333</v>
+        <v>492279</v>
       </c>
       <c r="R97" t="n">
-        <v>6678887</v>
+        <v>6678964</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12890,21 +12890,6 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ97" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK97" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO97" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12921,45 +12906,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128806459</v>
+        <v>128804682</v>
       </c>
       <c r="B98" t="n">
-        <v>91504</v>
+        <v>91716</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492279</v>
+        <v>492333</v>
       </c>
       <c r="R98" t="n">
-        <v>6678964</v>
+        <v>6678887</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -13002,6 +12987,21 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ98" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK98" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO98" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -13115,10 +13115,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B100" t="n">
-        <v>92232</v>
+        <v>91784</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13126,37 +13126,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R100" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13197,23 +13194,22 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13231,10 +13227,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805857</v>
+        <v>128805456</v>
       </c>
       <c r="B101" t="n">
-        <v>91784</v>
+        <v>92232</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13242,34 +13238,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1964</v>
+        <v>1105</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492381</v>
+        <v>492302</v>
       </c>
       <c r="R101" t="n">
-        <v>6678643</v>
+        <v>6678779</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13310,22 +13309,23 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13343,45 +13343,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128803412</v>
+        <v>128805191</v>
       </c>
       <c r="B102" t="n">
-        <v>92820</v>
+        <v>91958</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5448</v>
+        <v>1209</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492284</v>
+        <v>492220</v>
       </c>
       <c r="R102" t="n">
-        <v>6678978</v>
+        <v>6678844</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13440,45 +13440,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128805191</v>
+        <v>128803412</v>
       </c>
       <c r="B103" t="n">
-        <v>91958</v>
+        <v>92820</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
+        <v>5448</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492220</v>
+        <v>492284</v>
       </c>
       <c r="R103" t="n">
-        <v>6678844</v>
+        <v>6678978</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12596,10 +12596,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128805458</v>
+        <v>128803336</v>
       </c>
       <c r="B95" t="n">
-        <v>91914</v>
+        <v>92794</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12607,37 +12607,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4217</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492302</v>
+        <v>492306</v>
       </c>
       <c r="R95" t="n">
-        <v>6678779</v>
+        <v>6678952</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12678,24 +12675,8 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12712,10 +12693,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128803336</v>
+        <v>128805458</v>
       </c>
       <c r="B96" t="n">
-        <v>92794</v>
+        <v>91914</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12723,34 +12704,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492306</v>
+        <v>492302</v>
       </c>
       <c r="R96" t="n">
-        <v>6678952</v>
+        <v>6678779</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12791,8 +12775,24 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12809,45 +12809,45 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128806459</v>
+        <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91504</v>
+        <v>91716</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>1202</v>
+        <v>1106</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vågticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Osteina undosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Peck) Zmitr.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>492279</v>
+        <v>492333</v>
       </c>
       <c r="R97" t="n">
-        <v>6678964</v>
+        <v>6678887</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -12890,6 +12890,21 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ97" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK97" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO97" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
@@ -12906,45 +12921,45 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128804682</v>
+        <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91716</v>
+        <v>91504</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1106</v>
+        <v>1202</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vågticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Osteina undosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Peck) Zmitr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>492333</v>
+        <v>492279</v>
       </c>
       <c r="R98" t="n">
-        <v>6678887</v>
+        <v>6678964</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -12987,21 +13002,6 @@
       </c>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
@@ -13115,10 +13115,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805857</v>
+        <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>91784</v>
+        <v>92232</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13126,34 +13126,37 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1964</v>
+        <v>1105</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492381</v>
+        <v>492302</v>
       </c>
       <c r="R100" t="n">
-        <v>6678643</v>
+        <v>6678779</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13194,22 +13197,23 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13227,10 +13231,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>92232</v>
+        <v>91784</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13238,37 +13242,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R101" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13309,23 +13310,22 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13343,45 +13343,43 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805191</v>
+        <v>128805477</v>
       </c>
       <c r="B102" t="n">
-        <v>91958</v>
+        <v>91910</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492220</v>
+        <v>492302</v>
       </c>
       <c r="R102" t="n">
-        <v>6678844</v>
+        <v>6678779</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13422,8 +13420,24 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13440,45 +13454,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128803412</v>
+        <v>128805191</v>
       </c>
       <c r="B103" t="n">
-        <v>92820</v>
+        <v>91958</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5448</v>
+        <v>1209</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492284</v>
+        <v>492220</v>
       </c>
       <c r="R103" t="n">
-        <v>6678978</v>
+        <v>6678844</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13537,10 +13551,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805477</v>
+        <v>128803412</v>
       </c>
       <c r="B104" t="n">
-        <v>91910</v>
+        <v>92820</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13548,32 +13562,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492302</v>
+        <v>492284</v>
       </c>
       <c r="R104" t="n">
-        <v>6678779</v>
+        <v>6678978</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13614,24 +13630,8 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92823</v>
+        <v>92827</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90886</v>
+        <v>90890</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90886</v>
+        <v>90890</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12596,10 +12596,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128803336</v>
+        <v>128805458</v>
       </c>
       <c r="B95" t="n">
-        <v>92794</v>
+        <v>91918</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12607,34 +12607,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492306</v>
+        <v>492302</v>
       </c>
       <c r="R95" t="n">
-        <v>6678952</v>
+        <v>6678779</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12675,8 +12678,24 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12693,10 +12712,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128805458</v>
+        <v>128803336</v>
       </c>
       <c r="B96" t="n">
-        <v>91914</v>
+        <v>92798</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12704,37 +12723,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4217</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492302</v>
+        <v>492306</v>
       </c>
       <c r="R96" t="n">
-        <v>6678779</v>
+        <v>6678952</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12775,24 +12791,8 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12812,7 +12812,7 @@
         <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91716</v>
+        <v>91720</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91504</v>
+        <v>91508</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13018,45 +13018,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128803026</v>
+        <v>128805857</v>
       </c>
       <c r="B99" t="n">
-        <v>91504</v>
+        <v>91788</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492205</v>
+        <v>492381</v>
       </c>
       <c r="R99" t="n">
-        <v>6679020</v>
+        <v>6678643</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13099,6 +13099,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13115,48 +13130,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805456</v>
+        <v>128803026</v>
       </c>
       <c r="B100" t="n">
-        <v>92232</v>
+        <v>91508</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1105</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492302</v>
+        <v>492205</v>
       </c>
       <c r="R100" t="n">
-        <v>6678779</v>
+        <v>6679020</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13197,24 +13209,8 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13231,10 +13227,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805857</v>
+        <v>128805456</v>
       </c>
       <c r="B101" t="n">
-        <v>91784</v>
+        <v>92236</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13242,34 +13238,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1964</v>
+        <v>1105</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492381</v>
+        <v>492302</v>
       </c>
       <c r="R101" t="n">
-        <v>6678643</v>
+        <v>6678779</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13310,22 +13309,23 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13343,43 +13343,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805477</v>
+        <v>128805191</v>
       </c>
       <c r="B102" t="n">
-        <v>91910</v>
+        <v>91962</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6040162</v>
+        <v>1209</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492302</v>
+        <v>492220</v>
       </c>
       <c r="R102" t="n">
-        <v>6678779</v>
+        <v>6678844</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13420,24 +13422,8 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13454,45 +13440,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128805191</v>
+        <v>128803412</v>
       </c>
       <c r="B103" t="n">
-        <v>91958</v>
+        <v>92824</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
+        <v>5448</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492220</v>
+        <v>492284</v>
       </c>
       <c r="R103" t="n">
-        <v>6678844</v>
+        <v>6678978</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13551,10 +13537,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128803412</v>
+        <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>92820</v>
+        <v>91914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13562,34 +13548,32 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492284</v>
+        <v>492302</v>
       </c>
       <c r="R104" t="n">
-        <v>6678978</v>
+        <v>6678779</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13630,8 +13614,24 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -13651,7 +13651,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96878</v>
+        <v>96882</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>128805579</v>
       </c>
       <c r="B106" t="n">
-        <v>80098</v>
+        <v>80102</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>128806246</v>
       </c>
       <c r="B107" t="n">
-        <v>86760</v>
+        <v>86764</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -13018,45 +13018,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128805857</v>
+        <v>128803026</v>
       </c>
       <c r="B99" t="n">
-        <v>91788</v>
+        <v>91508</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1964</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492381</v>
+        <v>492205</v>
       </c>
       <c r="R99" t="n">
-        <v>6678643</v>
+        <v>6679020</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13099,21 +13099,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13130,45 +13115,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128803026</v>
+        <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>91508</v>
+        <v>92236</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492205</v>
+        <v>492302</v>
       </c>
       <c r="R100" t="n">
-        <v>6679020</v>
+        <v>6678779</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13209,8 +13197,24 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13227,10 +13231,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>92236</v>
+        <v>91788</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13238,37 +13242,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R101" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13309,23 +13310,22 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13343,45 +13343,43 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805191</v>
+        <v>128805477</v>
       </c>
       <c r="B102" t="n">
-        <v>91962</v>
+        <v>91914</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492220</v>
+        <v>492302</v>
       </c>
       <c r="R102" t="n">
-        <v>6678844</v>
+        <v>6678779</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13422,8 +13420,24 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13440,45 +13454,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128803412</v>
+        <v>128805191</v>
       </c>
       <c r="B103" t="n">
-        <v>92824</v>
+        <v>91962</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5448</v>
+        <v>1209</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492284</v>
+        <v>492220</v>
       </c>
       <c r="R103" t="n">
-        <v>6678978</v>
+        <v>6678844</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13537,10 +13551,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805477</v>
+        <v>128803412</v>
       </c>
       <c r="B104" t="n">
-        <v>91914</v>
+        <v>92824</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13548,32 +13562,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492302</v>
+        <v>492284</v>
       </c>
       <c r="R104" t="n">
-        <v>6678779</v>
+        <v>6678978</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13614,24 +13630,8 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -13018,45 +13018,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128803026</v>
+        <v>128805857</v>
       </c>
       <c r="B99" t="n">
-        <v>91508</v>
+        <v>91788</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492205</v>
+        <v>492381</v>
       </c>
       <c r="R99" t="n">
-        <v>6679020</v>
+        <v>6678643</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13099,6 +13099,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13115,48 +13130,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805456</v>
+        <v>128803026</v>
       </c>
       <c r="B100" t="n">
-        <v>92236</v>
+        <v>91508</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1105</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492302</v>
+        <v>492205</v>
       </c>
       <c r="R100" t="n">
-        <v>6678779</v>
+        <v>6679020</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13197,24 +13209,8 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13231,10 +13227,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805857</v>
+        <v>128805456</v>
       </c>
       <c r="B101" t="n">
-        <v>91788</v>
+        <v>92236</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13242,34 +13238,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1964</v>
+        <v>1105</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492381</v>
+        <v>492302</v>
       </c>
       <c r="R101" t="n">
-        <v>6678643</v>
+        <v>6678779</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13310,22 +13309,23 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13343,43 +13343,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805477</v>
+        <v>128805191</v>
       </c>
       <c r="B102" t="n">
-        <v>91914</v>
+        <v>91962</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6040162</v>
+        <v>1209</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492302</v>
+        <v>492220</v>
       </c>
       <c r="R102" t="n">
-        <v>6678779</v>
+        <v>6678844</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13420,24 +13422,8 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13454,45 +13440,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128805191</v>
+        <v>128803412</v>
       </c>
       <c r="B103" t="n">
-        <v>91962</v>
+        <v>92824</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
+        <v>5448</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492220</v>
+        <v>492284</v>
       </c>
       <c r="R103" t="n">
-        <v>6678844</v>
+        <v>6678978</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13551,10 +13537,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128803412</v>
+        <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>92824</v>
+        <v>91914</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13562,34 +13548,32 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492284</v>
+        <v>492302</v>
       </c>
       <c r="R104" t="n">
-        <v>6678978</v>
+        <v>6678779</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13630,8 +13614,24 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92827</v>
+        <v>92832</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90890</v>
+        <v>90895</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90890</v>
+        <v>90895</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12596,10 +12596,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128805458</v>
+        <v>128803336</v>
       </c>
       <c r="B95" t="n">
-        <v>91918</v>
+        <v>92803</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12607,37 +12607,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4217</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492302</v>
+        <v>492306</v>
       </c>
       <c r="R95" t="n">
-        <v>6678779</v>
+        <v>6678952</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12678,24 +12675,8 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12712,10 +12693,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128803336</v>
+        <v>128805458</v>
       </c>
       <c r="B96" t="n">
-        <v>92798</v>
+        <v>91923</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12723,34 +12704,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492306</v>
+        <v>492302</v>
       </c>
       <c r="R96" t="n">
-        <v>6678952</v>
+        <v>6678779</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12791,8 +12775,24 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12812,7 +12812,7 @@
         <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91720</v>
+        <v>91725</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13018,45 +13018,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128805857</v>
+        <v>128803026</v>
       </c>
       <c r="B99" t="n">
-        <v>91788</v>
+        <v>91513</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1964</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492381</v>
+        <v>492205</v>
       </c>
       <c r="R99" t="n">
-        <v>6678643</v>
+        <v>6679020</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13099,21 +13099,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13130,45 +13115,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128803026</v>
+        <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>91508</v>
+        <v>92241</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492205</v>
+        <v>492302</v>
       </c>
       <c r="R100" t="n">
-        <v>6679020</v>
+        <v>6678779</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13209,8 +13197,24 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13227,10 +13231,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>92236</v>
+        <v>91793</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13238,37 +13242,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R101" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13309,23 +13310,22 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13346,7 +13346,7 @@
         <v>128805191</v>
       </c>
       <c r="B102" t="n">
-        <v>91962</v>
+        <v>91967</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>128803412</v>
       </c>
       <c r="B103" t="n">
-        <v>92824</v>
+        <v>92829</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>91914</v>
+        <v>91919</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96882</v>
+        <v>96889</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>128805579</v>
       </c>
       <c r="B106" t="n">
-        <v>80102</v>
+        <v>80007</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>128806246</v>
       </c>
       <c r="B107" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92840</v>
+        <v>92845</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90902</v>
+        <v>90905</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90902</v>
+        <v>90905</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>128805458</v>
       </c>
       <c r="B95" t="n">
-        <v>91931</v>
+        <v>91934</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>128803336</v>
       </c>
       <c r="B96" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91732</v>
+        <v>91735</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>128803026</v>
       </c>
       <c r="B99" t="n">
-        <v>91520</v>
+        <v>91523</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>92249</v>
+        <v>92254</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>91798</v>
+        <v>91801</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13343,10 +13343,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128803412</v>
+        <v>128805477</v>
       </c>
       <c r="B102" t="n">
-        <v>92837</v>
+        <v>91930</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13354,34 +13354,32 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492284</v>
+        <v>492302</v>
       </c>
       <c r="R102" t="n">
-        <v>6678978</v>
+        <v>6678779</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13422,8 +13420,24 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13443,7 +13457,7 @@
         <v>128805191</v>
       </c>
       <c r="B103" t="n">
-        <v>91975</v>
+        <v>91978</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13537,10 +13551,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805477</v>
+        <v>128803412</v>
       </c>
       <c r="B104" t="n">
-        <v>91927</v>
+        <v>92842</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13548,32 +13562,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492302</v>
+        <v>492284</v>
       </c>
       <c r="R104" t="n">
-        <v>6678779</v>
+        <v>6678978</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13614,24 +13630,8 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -13651,7 +13651,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96897</v>
+        <v>96902</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>128806246</v>
       </c>
       <c r="B107" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92845</v>
+        <v>92848</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90905</v>
+        <v>90908</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90905</v>
+        <v>90908</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>128805458</v>
       </c>
       <c r="B95" t="n">
-        <v>91934</v>
+        <v>91937</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>128803336</v>
       </c>
       <c r="B96" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91735</v>
+        <v>91738</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13021,7 +13021,7 @@
         <v>128803026</v>
       </c>
       <c r="B99" t="n">
-        <v>91523</v>
+        <v>91526</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13118,7 +13118,7 @@
         <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>92254</v>
+        <v>92257</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13234,7 +13234,7 @@
         <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>91801</v>
+        <v>91804</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13343,43 +13343,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805477</v>
+        <v>128805191</v>
       </c>
       <c r="B102" t="n">
-        <v>91930</v>
+        <v>91981</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6040162</v>
+        <v>1209</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492302</v>
+        <v>492220</v>
       </c>
       <c r="R102" t="n">
-        <v>6678779</v>
+        <v>6678844</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13420,24 +13422,8 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13454,45 +13440,43 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128805191</v>
+        <v>128805477</v>
       </c>
       <c r="B103" t="n">
-        <v>91978</v>
+        <v>91933</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492220</v>
+        <v>492302</v>
       </c>
       <c r="R103" t="n">
-        <v>6678844</v>
+        <v>6678779</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13533,8 +13517,24 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13554,7 +13554,7 @@
         <v>128803412</v>
       </c>
       <c r="B104" t="n">
-        <v>92842</v>
+        <v>92845</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96902</v>
+        <v>96905</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>128805579</v>
       </c>
       <c r="B106" t="n">
-        <v>80012</v>
+        <v>80013</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>128806246</v>
       </c>
       <c r="B107" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -13018,45 +13018,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128803026</v>
+        <v>128805857</v>
       </c>
       <c r="B99" t="n">
-        <v>91526</v>
+        <v>91804</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492205</v>
+        <v>492381</v>
       </c>
       <c r="R99" t="n">
-        <v>6679020</v>
+        <v>6678643</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13099,6 +13099,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13115,48 +13130,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805456</v>
+        <v>128803026</v>
       </c>
       <c r="B100" t="n">
-        <v>92257</v>
+        <v>91526</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1105</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492302</v>
+        <v>492205</v>
       </c>
       <c r="R100" t="n">
-        <v>6678779</v>
+        <v>6679020</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13197,24 +13209,8 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13231,10 +13227,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805857</v>
+        <v>128805456</v>
       </c>
       <c r="B101" t="n">
-        <v>91804</v>
+        <v>92257</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13242,34 +13238,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1964</v>
+        <v>1105</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492381</v>
+        <v>492302</v>
       </c>
       <c r="R101" t="n">
-        <v>6678643</v>
+        <v>6678779</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13310,22 +13309,23 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13440,10 +13440,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128805477</v>
+        <v>128803412</v>
       </c>
       <c r="B103" t="n">
-        <v>91933</v>
+        <v>92845</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13451,32 +13451,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492302</v>
+        <v>492284</v>
       </c>
       <c r="R103" t="n">
-        <v>6678779</v>
+        <v>6678978</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13517,24 +13519,8 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13551,10 +13537,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128803412</v>
+        <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>92845</v>
+        <v>91933</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13562,34 +13548,32 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492284</v>
+        <v>492302</v>
       </c>
       <c r="R104" t="n">
-        <v>6678978</v>
+        <v>6678779</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13630,8 +13614,24 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -13018,10 +13018,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128805857</v>
+        <v>128805456</v>
       </c>
       <c r="B99" t="n">
-        <v>91804</v>
+        <v>92257</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13029,34 +13029,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1964</v>
+        <v>1105</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492381</v>
+        <v>492302</v>
       </c>
       <c r="R99" t="n">
-        <v>6678643</v>
+        <v>6678779</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13097,22 +13100,23 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13227,10 +13231,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>92257</v>
+        <v>91804</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13238,37 +13242,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R101" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13309,23 +13310,22 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13440,10 +13440,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128803412</v>
+        <v>128805477</v>
       </c>
       <c r="B103" t="n">
-        <v>92845</v>
+        <v>91933</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13451,34 +13451,32 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492284</v>
+        <v>492302</v>
       </c>
       <c r="R103" t="n">
-        <v>6678978</v>
+        <v>6678779</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13519,8 +13517,24 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13537,10 +13551,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805477</v>
+        <v>128803412</v>
       </c>
       <c r="B104" t="n">
-        <v>91933</v>
+        <v>92845</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13548,32 +13562,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492302</v>
+        <v>492284</v>
       </c>
       <c r="R104" t="n">
-        <v>6678779</v>
+        <v>6678978</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13614,24 +13630,8 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92848</v>
+        <v>92855</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90908</v>
+        <v>90912</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90908</v>
+        <v>90912</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>128805458</v>
       </c>
       <c r="B95" t="n">
-        <v>91937</v>
+        <v>91944</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>128803336</v>
       </c>
       <c r="B96" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91738</v>
+        <v>91745</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13018,48 +13018,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128805456</v>
+        <v>128803026</v>
       </c>
       <c r="B99" t="n">
-        <v>92257</v>
+        <v>91533</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1105</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492302</v>
+        <v>492205</v>
       </c>
       <c r="R99" t="n">
-        <v>6678779</v>
+        <v>6679020</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13100,24 +13097,8 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13134,45 +13115,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128803026</v>
+        <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>91526</v>
+        <v>92264</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492205</v>
+        <v>492302</v>
       </c>
       <c r="R100" t="n">
-        <v>6679020</v>
+        <v>6678779</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13213,8 +13197,24 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13234,7 +13234,7 @@
         <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>91804</v>
+        <v>91811</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13346,7 +13346,7 @@
         <v>128805191</v>
       </c>
       <c r="B102" t="n">
-        <v>91981</v>
+        <v>91988</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13440,10 +13440,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128805477</v>
+        <v>128803412</v>
       </c>
       <c r="B103" t="n">
-        <v>91933</v>
+        <v>92852</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13451,32 +13451,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492302</v>
+        <v>492284</v>
       </c>
       <c r="R103" t="n">
-        <v>6678779</v>
+        <v>6678978</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13517,24 +13519,8 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13551,10 +13537,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128803412</v>
+        <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>92845</v>
+        <v>91940</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13562,34 +13548,32 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492284</v>
+        <v>492302</v>
       </c>
       <c r="R104" t="n">
-        <v>6678978</v>
+        <v>6678779</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13630,8 +13614,24 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -13651,7 +13651,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96905</v>
+        <v>96915</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>128805579</v>
       </c>
       <c r="B106" t="n">
-        <v>80013</v>
+        <v>80017</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>128806246</v>
       </c>
       <c r="B107" t="n">
-        <v>86782</v>
+        <v>86786</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90912</v>
+        <v>90919</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90912</v>
+        <v>90919</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12596,10 +12596,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128805458</v>
+        <v>128803336</v>
       </c>
       <c r="B95" t="n">
-        <v>91944</v>
+        <v>92833</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12607,37 +12607,34 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4217</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
-      <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr"/>
-      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492302</v>
+        <v>492306</v>
       </c>
       <c r="R95" t="n">
-        <v>6678779</v>
+        <v>6678952</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12678,24 +12675,8 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
-      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ95" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO95" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12712,10 +12693,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128803336</v>
+        <v>128805458</v>
       </c>
       <c r="B96" t="n">
-        <v>92826</v>
+        <v>91951</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12723,34 +12704,37 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="J96" t="inlineStr"/>
+      <c r="K96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492306</v>
+        <v>492302</v>
       </c>
       <c r="R96" t="n">
-        <v>6678952</v>
+        <v>6678779</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12791,8 +12775,24 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
+      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ96" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO96" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12812,7 +12812,7 @@
         <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91745</v>
+        <v>91752</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13018,45 +13018,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128803026</v>
+        <v>128805857</v>
       </c>
       <c r="B99" t="n">
-        <v>91533</v>
+        <v>91818</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492205</v>
+        <v>492381</v>
       </c>
       <c r="R99" t="n">
-        <v>6679020</v>
+        <v>6678643</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13099,6 +13099,21 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>asp</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Populus tremula</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13115,48 +13130,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805456</v>
+        <v>128803026</v>
       </c>
       <c r="B100" t="n">
-        <v>92264</v>
+        <v>91540</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1105</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492302</v>
+        <v>492205</v>
       </c>
       <c r="R100" t="n">
-        <v>6678779</v>
+        <v>6679020</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13197,24 +13209,8 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13231,10 +13227,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805857</v>
+        <v>128805456</v>
       </c>
       <c r="B101" t="n">
-        <v>91811</v>
+        <v>92271</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13242,34 +13238,37 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1964</v>
+        <v>1105</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492381</v>
+        <v>492302</v>
       </c>
       <c r="R101" t="n">
-        <v>6678643</v>
+        <v>6678779</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13310,22 +13309,23 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>asp</t>
+          <t>tall</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Populus tremula</t>
+          <t>Pinus sylvestris</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13346,7 +13346,7 @@
         <v>128805191</v>
       </c>
       <c r="B102" t="n">
-        <v>91988</v>
+        <v>91995</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>128803412</v>
       </c>
       <c r="B103" t="n">
-        <v>92852</v>
+        <v>92859</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>91940</v>
+        <v>91947</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96915</v>
+        <v>96922</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>128806246</v>
       </c>
       <c r="B107" t="n">
-        <v>86786</v>
+        <v>86793</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92862</v>
+        <v>92864</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90919</v>
+        <v>90921</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90919</v>
+        <v>90921</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12596,10 +12596,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128803336</v>
+        <v>128805458</v>
       </c>
       <c r="B95" t="n">
-        <v>92833</v>
+        <v>91953</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12607,34 +12607,37 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>4217</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
+      <c r="K95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>492306</v>
+        <v>492302</v>
       </c>
       <c r="R95" t="n">
-        <v>6678952</v>
+        <v>6678779</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -12675,8 +12678,24 @@
       <c r="AE95" t="b">
         <v>0</v>
       </c>
+      <c r="AF95" t="inlineStr"/>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ95" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO95" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
@@ -12693,10 +12712,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128805458</v>
+        <v>128803336</v>
       </c>
       <c r="B96" t="n">
-        <v>91951</v>
+        <v>92835</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12704,37 +12723,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>4217</v>
+        <v>4364</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Blodticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Meruliopsis taxicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Pers.:Fr.) Bondartsev</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
-      <c r="J96" t="inlineStr"/>
-      <c r="K96" t="inlineStr"/>
-      <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>492302</v>
+        <v>492306</v>
       </c>
       <c r="R96" t="n">
-        <v>6678779</v>
+        <v>6678952</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -12775,24 +12791,8 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ96" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO96" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
@@ -12812,7 +12812,7 @@
         <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91752</v>
+        <v>91754</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91540</v>
+        <v>91542</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13018,45 +13018,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128805857</v>
+        <v>128803026</v>
       </c>
       <c r="B99" t="n">
-        <v>91818</v>
+        <v>91542</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1964</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492381</v>
+        <v>492205</v>
       </c>
       <c r="R99" t="n">
-        <v>6678643</v>
+        <v>6679020</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13099,21 +13099,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13130,45 +13115,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128803026</v>
+        <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>91540</v>
+        <v>92273</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492205</v>
+        <v>492302</v>
       </c>
       <c r="R100" t="n">
-        <v>6679020</v>
+        <v>6678779</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13209,8 +13197,24 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13227,10 +13231,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>92271</v>
+        <v>91820</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13238,37 +13242,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R101" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13309,23 +13310,22 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13346,7 +13346,7 @@
         <v>128805191</v>
       </c>
       <c r="B102" t="n">
-        <v>91995</v>
+        <v>91997</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13443,7 +13443,7 @@
         <v>128803412</v>
       </c>
       <c r="B103" t="n">
-        <v>92859</v>
+        <v>92861</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13540,7 +13540,7 @@
         <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>91947</v>
+        <v>91949</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13651,7 +13651,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96922</v>
+        <v>96924</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13748,7 +13748,7 @@
         <v>128805579</v>
       </c>
       <c r="B106" t="n">
-        <v>80017</v>
+        <v>80019</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>128806246</v>
       </c>
       <c r="B107" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -13018,45 +13018,48 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128803026</v>
+        <v>128805456</v>
       </c>
       <c r="B99" t="n">
-        <v>91542</v>
+        <v>92273</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
+      <c r="J99" t="inlineStr"/>
+      <c r="K99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492205</v>
+        <v>492302</v>
       </c>
       <c r="R99" t="n">
-        <v>6679020</v>
+        <v>6678779</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13097,8 +13100,24 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
+      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13115,10 +13134,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B100" t="n">
-        <v>92273</v>
+        <v>91820</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -13126,37 +13145,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr"/>
-      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R100" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13197,23 +13213,22 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
-      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
       </c>
       <c r="AJ100" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK100" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT100" t="inlineStr"/>
@@ -13231,45 +13246,45 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805857</v>
+        <v>128803026</v>
       </c>
       <c r="B101" t="n">
-        <v>91820</v>
+        <v>91542</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1964</v>
+        <v>1202</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492381</v>
+        <v>492205</v>
       </c>
       <c r="R101" t="n">
-        <v>6678643</v>
+        <v>6679020</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13312,21 +13327,6 @@
       </c>
       <c r="AG101" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ101" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK101" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO101" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13343,45 +13343,43 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805191</v>
+        <v>128805477</v>
       </c>
       <c r="B102" t="n">
-        <v>91997</v>
+        <v>91949</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
+      <c r="J102" t="inlineStr"/>
+      <c r="K102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492220</v>
+        <v>492302</v>
       </c>
       <c r="R102" t="n">
-        <v>6678844</v>
+        <v>6678779</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13422,8 +13420,24 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
+      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ102" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13440,45 +13454,45 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128803412</v>
+        <v>128805191</v>
       </c>
       <c r="B103" t="n">
-        <v>92861</v>
+        <v>91997</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5448</v>
+        <v>1209</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Phlebia centrifuga</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492284</v>
+        <v>492220</v>
       </c>
       <c r="R103" t="n">
-        <v>6678978</v>
+        <v>6678844</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13537,10 +13551,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805477</v>
+        <v>128803412</v>
       </c>
       <c r="B104" t="n">
-        <v>91949</v>
+        <v>92861</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13548,32 +13562,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492302</v>
+        <v>492284</v>
       </c>
       <c r="R104" t="n">
-        <v>6678779</v>
+        <v>6678978</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13614,24 +13630,8 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ104" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO104" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92864</v>
+        <v>92850</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12405,7 +12405,7 @@
         <v>128802766</v>
       </c>
       <c r="B93" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -12502,7 +12502,7 @@
         <v>128804210</v>
       </c>
       <c r="B94" t="n">
-        <v>90921</v>
+        <v>90922</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -12599,7 +12599,7 @@
         <v>128805458</v>
       </c>
       <c r="B95" t="n">
-        <v>91953</v>
+        <v>91962</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12715,7 +12715,7 @@
         <v>128803336</v>
       </c>
       <c r="B96" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12812,7 +12812,7 @@
         <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91754</v>
+        <v>91763</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -12924,7 +12924,7 @@
         <v>128806459</v>
       </c>
       <c r="B98" t="n">
-        <v>91542</v>
+        <v>91540</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -13018,10 +13018,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B99" t="n">
-        <v>92273</v>
+        <v>91830</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -13029,37 +13029,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="J99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="N99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R99" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13100,23 +13097,22 @@
       <c r="AE99" t="b">
         <v>0</v>
       </c>
-      <c r="AF99" t="inlineStr"/>
       <c r="AG99" t="b">
         <v>0</v>
       </c>
       <c r="AJ99" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK99" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT99" t="inlineStr"/>
@@ -13134,45 +13130,45 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128805857</v>
+        <v>128803026</v>
       </c>
       <c r="B100" t="n">
-        <v>91820</v>
+        <v>91540</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1964</v>
+        <v>1202</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492381</v>
+        <v>492205</v>
       </c>
       <c r="R100" t="n">
-        <v>6678643</v>
+        <v>6679020</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13215,21 +13211,6 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ100" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK100" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO100" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13246,45 +13227,48 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128803026</v>
+        <v>128805456</v>
       </c>
       <c r="B101" t="n">
-        <v>91542</v>
+        <v>92287</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
+      <c r="K101" t="inlineStr"/>
+      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492205</v>
+        <v>492302</v>
       </c>
       <c r="R101" t="n">
-        <v>6679020</v>
+        <v>6678779</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13325,8 +13309,24 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
+      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
@@ -13343,10 +13343,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128805477</v>
+        <v>128803412</v>
       </c>
       <c r="B102" t="n">
-        <v>91949</v>
+        <v>92847</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -13354,32 +13354,34 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
-      <c r="J102" t="inlineStr"/>
-      <c r="K102" t="inlineStr"/>
-      <c r="N102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492302</v>
+        <v>492284</v>
       </c>
       <c r="R102" t="n">
-        <v>6678779</v>
+        <v>6678978</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13420,24 +13422,8 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ102" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO102" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
@@ -13454,45 +13440,43 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128805191</v>
+        <v>128805477</v>
       </c>
       <c r="B103" t="n">
-        <v>91997</v>
+        <v>91957</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>1209</v>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>Rynkskinn</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492220</v>
+        <v>492302</v>
       </c>
       <c r="R103" t="n">
-        <v>6678844</v>
+        <v>6678779</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13533,8 +13517,24 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
+      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ103" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13551,45 +13551,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128803412</v>
+        <v>128805191</v>
       </c>
       <c r="B104" t="n">
-        <v>92861</v>
+        <v>91992</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5448</v>
+        <v>1209</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492284</v>
+        <v>492220</v>
       </c>
       <c r="R104" t="n">
-        <v>6678978</v>
+        <v>6678844</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13651,7 +13651,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96924</v>
+        <v>96950</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -13860,7 +13860,7 @@
         <v>128806246</v>
       </c>
       <c r="B107" t="n">
-        <v>86795</v>
+        <v>86796</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12317,7 +12317,7 @@
         <v>128803366</v>
       </c>
       <c r="B92" t="n">
-        <v>92850</v>
+        <v>92851</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -12327,9 +12327,14 @@
       <c r="E92" t="n">
         <v>5449</v>
       </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Svart taggsvamp agg.</t>
+        </is>
+      </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Phellodon niger s.lat</t>
+          <t>Phellodon niger s.lat.</t>
         </is>
       </c>
       <c r="H92" t="inlineStr"/>
@@ -12599,7 +12604,7 @@
         <v>128805458</v>
       </c>
       <c r="B95" t="n">
-        <v>91962</v>
+        <v>91963</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -12715,7 +12720,7 @@
         <v>128803336</v>
       </c>
       <c r="B96" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -12812,7 +12817,7 @@
         <v>128804682</v>
       </c>
       <c r="B97" t="n">
-        <v>91763</v>
+        <v>91764</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -13018,45 +13023,45 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128805857</v>
+        <v>128803026</v>
       </c>
       <c r="B99" t="n">
-        <v>91830</v>
+        <v>91540</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>1964</v>
+        <v>1202</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Honungsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Fomitopsis mellita</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Norsbodarna, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>492381</v>
+        <v>492205</v>
       </c>
       <c r="R99" t="n">
-        <v>6678643</v>
+        <v>6679020</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -13099,21 +13104,6 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>asp</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>Populus tremula</t>
-        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
@@ -13130,45 +13120,48 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128803026</v>
+        <v>128805456</v>
       </c>
       <c r="B100" t="n">
-        <v>91540</v>
+        <v>92288</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1202</v>
+        <v>1105</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Laxporing</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodonia placenta</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="J100" t="inlineStr"/>
+      <c r="K100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>492205</v>
+        <v>492302</v>
       </c>
       <c r="R100" t="n">
-        <v>6679020</v>
+        <v>6678779</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -13209,8 +13202,24 @@
       <c r="AE100" t="b">
         <v>0</v>
       </c>
+      <c r="AF100" t="inlineStr"/>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ100" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
@@ -13227,10 +13236,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128805456</v>
+        <v>128805857</v>
       </c>
       <c r="B101" t="n">
-        <v>92287</v>
+        <v>91831</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -13238,37 +13247,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1105</v>
+        <v>1964</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Laxporing</t>
+          <t>Honungsticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Rhodonia placenta</t>
+          <t>Fomitopsis mellita</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä, K.H.Larss. &amp; Schigel</t>
+          <t>(Niemelä &amp; Penttilä) Niemelä &amp; Miettinen</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="J101" t="inlineStr"/>
-      <c r="K101" t="inlineStr"/>
-      <c r="N101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsbodarna, Dlr</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>492302</v>
+        <v>492381</v>
       </c>
       <c r="R101" t="n">
-        <v>6678779</v>
+        <v>6678643</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -13309,23 +13315,22 @@
       <c r="AE101" t="b">
         <v>0</v>
       </c>
-      <c r="AF101" t="inlineStr"/>
       <c r="AG101" t="b">
         <v>0</v>
       </c>
       <c r="AJ101" t="inlineStr">
         <is>
-          <t>tall</t>
+          <t>asp</t>
         </is>
       </c>
       <c r="AK101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>Pinus sylvestris</t>
+          <t>Populus tremula</t>
         </is>
       </c>
       <c r="AT101" t="inlineStr"/>
@@ -13343,45 +13348,45 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128803412</v>
+        <v>128805191</v>
       </c>
       <c r="B102" t="n">
-        <v>92847</v>
+        <v>91993</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5448</v>
+        <v>1209</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>492284</v>
+        <v>492220</v>
       </c>
       <c r="R102" t="n">
-        <v>6678978</v>
+        <v>6678844</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -13443,7 +13448,7 @@
         <v>128805477</v>
       </c>
       <c r="B103" t="n">
-        <v>91957</v>
+        <v>91958</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13551,45 +13556,45 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128805191</v>
+        <v>128803412</v>
       </c>
       <c r="B104" t="n">
-        <v>91992</v>
+        <v>92848</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>1209</v>
+        <v>5448</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492220</v>
+        <v>492284</v>
       </c>
       <c r="R104" t="n">
-        <v>6678844</v>
+        <v>6678978</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13651,7 +13656,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96950</v>
+        <v>96951</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -13445,10 +13445,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128805477</v>
+        <v>128803412</v>
       </c>
       <c r="B103" t="n">
-        <v>91958</v>
+        <v>92848</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -13456,32 +13456,34 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6040162</v>
+        <v>5448</v>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Leptoporus erubescens</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.) Bourdot &amp; Galzin</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="N103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Norsådammen, Dlr</t>
+          <t>Norsdammen, Dlr</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>492302</v>
+        <v>492284</v>
       </c>
       <c r="R103" t="n">
-        <v>6678779</v>
+        <v>6678978</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -13522,24 +13524,8 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ103" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AO103" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
       </c>
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
@@ -13556,10 +13542,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128803412</v>
+        <v>128805477</v>
       </c>
       <c r="B104" t="n">
-        <v>92848</v>
+        <v>91958</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -13567,34 +13553,32 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>5448</v>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>Svartvit taggsvamp</t>
-        </is>
+        <v>6040162</v>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Leptoporus erubescens</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Fr.) Bourdot &amp; Galzin</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norsdammen, Dlr</t>
+          <t>Norsådammen, Dlr</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>492284</v>
+        <v>492302</v>
       </c>
       <c r="R104" t="n">
-        <v>6678978</v>
+        <v>6678779</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -13635,8 +13619,24 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
+      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ104" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
@@ -13656,7 +13656,7 @@
         <v>128803288</v>
       </c>
       <c r="B105" t="n">
-        <v>96951</v>
+        <v>96952</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91859</v>
+        <v>91977</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12271,7 +12271,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Väntar på mikroskopering.</t>
+          <t>Mikroskoperad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -12280,7 +12280,11 @@
       <c r="AE91" t="b">
         <v>0</v>
       </c>
-      <c r="AF91" t="inlineStr"/>
+      <c r="AF91" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG91" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91977</v>
+        <v>91980</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -12210,6 +12210,11 @@
       </c>
       <c r="E91" t="n">
         <v>233025</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Lusporing</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -12271,7 +12276,7 @@
       </c>
       <c r="AC91" t="inlineStr">
         <is>
-          <t>Mikroskoperad av Janolof Hermansson.</t>
+          <t>På brunrötad granlåga i fuktig granskog. Mikroskoperad av Janolof Hermansson.</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91980</v>
+        <v>91983</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91983</v>
+        <v>91984</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>91984</v>
+        <v>92001</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>92017</v>
+        <v>92019</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -12201,7 +12201,7 @@
         <v>127478884</v>
       </c>
       <c r="B91" t="n">
-        <v>92019</v>
+        <v>92106</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>

--- a/artfynd/A 7605-2024 artfynd.xlsx
+++ b/artfynd/A 7605-2024 artfynd.xlsx
@@ -13322,7 +13322,7 @@
         <v>0</v>
       </c>
       <c r="AE101" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG101" t="b">
         <v>0</v>
